--- a/ROSA_vitaSPEC/Results/test_pretraitements/ratio.alpha.beta/Resultats_ratio.alpha.beta_moy_diff.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/ratio.alpha.beta/Resultats_ratio.alpha.beta_moy_diff.xlsx
@@ -1,217 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U108-N806\Documents\STAGE_M2_ROSA_NIRS\VitaSPEC\vitaspec_R\ROSA_vitaSPEC\Results\test_pretraitements\ratio.alpha.beta\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
-  <si>
-    <t>Pretraitement</t>
-  </si>
-  <si>
-    <t>LV1_diff</t>
-  </si>
-  <si>
-    <t>LV2_diff</t>
-  </si>
-  <si>
-    <t>LV3_diff</t>
-  </si>
-  <si>
-    <t>LV4_diff</t>
-  </si>
-  <si>
-    <t>LV5_diff</t>
-  </si>
-  <si>
-    <t>LV6_diff</t>
-  </si>
-  <si>
-    <t>LV7_diff</t>
-  </si>
-  <si>
-    <t>LV8_diff</t>
-  </si>
-  <si>
-    <t>LV9_diff</t>
-  </si>
-  <si>
-    <t>LV10_diff</t>
-  </si>
-  <si>
-    <t>LV11_diff</t>
-  </si>
-  <si>
-    <t>LV12_diff</t>
-  </si>
-  <si>
-    <t>LV13_diff</t>
-  </si>
-  <si>
-    <t>LV14_diff</t>
-  </si>
-  <si>
-    <t>LV15_diff</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1000,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,20,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,20,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,750,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,750,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_snv_sder_c(1,3,5)_</t>
-  </si>
-  <si>
-    <t>adj_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -257,72 +61,13 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -364,7 +109,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -396,10 +141,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -431,7 +175,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -607,2373 +350,2485 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:P47"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="51.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="16" width="12" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>16</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Pretraitement</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>LV1_diff</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>LV2_diff</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>LV3_diff</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>LV4_diff</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>LV5_diff</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>LV6_diff</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>LV7_diff</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>LV8_diff</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>LV9_diff</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>LV10_diff</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>LV11_diff</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>LV12_diff</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>LV13_diff</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>LV14_diff</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>LV15_diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1000,1)_snv_</t>
+        </is>
       </c>
       <c r="B2">
-        <v>4.0074769806378162E-2</v>
+        <v>0.03904797754217491</v>
       </c>
       <c r="C2">
-        <v>8.1823618045225116E-2</v>
+        <v>0.08538607163223653</v>
       </c>
       <c r="D2">
-        <v>0.1170419782216338</v>
+        <v>0.1207489735083802</v>
       </c>
       <c r="E2">
-        <v>0.1538292628055925</v>
+        <v>0.1583339649746449</v>
       </c>
       <c r="F2">
-        <v>0.18476879841565891</v>
+        <v>0.1838849101104164</v>
       </c>
       <c r="G2">
-        <v>0.27951942489761089</v>
+        <v>0.2755525823304284</v>
       </c>
       <c r="H2">
-        <v>0.2438466619959555</v>
+        <v>0.2502968322657916</v>
       </c>
       <c r="I2">
-        <v>0.25842541578735262</v>
+        <v>0.2614822225720915</v>
       </c>
       <c r="J2">
-        <v>0.35301424668978748</v>
+        <v>0.3485429813421914</v>
       </c>
       <c r="K2">
-        <v>0.35759593695376563</v>
+        <v>0.3619292792684995</v>
       </c>
       <c r="L2">
-        <v>0.38030399071750948</v>
+        <v>0.3882838349995015</v>
       </c>
       <c r="M2">
-        <v>0.39436848008048031</v>
+        <v>0.4034051666227304</v>
       </c>
       <c r="N2">
-        <v>0.40007230449584469</v>
+        <v>0.4066413927126138</v>
       </c>
       <c r="O2">
-        <v>0.39831784521248492</v>
+        <v>0.4037438123486587</v>
       </c>
       <c r="P2">
-        <v>0.37574928332044111</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>17</v>
+        <v>0.3746381475628773</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B3">
-        <v>6.3175628536727507E-2</v>
+        <v>0.06237217781579563</v>
       </c>
       <c r="C3">
-        <v>0.11871648045788941</v>
+        <v>0.1112077138765986</v>
       </c>
       <c r="D3">
-        <v>0.52393908367890951</v>
+        <v>0.5186837485391209</v>
       </c>
       <c r="E3">
-        <v>0.3749549450650968</v>
+        <v>0.3653780361348797</v>
       </c>
       <c r="F3">
-        <v>0.36280136338977909</v>
+        <v>0.3504825275394348</v>
       </c>
       <c r="G3">
-        <v>0.33176289695387939</v>
+        <v>0.334272156613693</v>
       </c>
       <c r="H3">
-        <v>0.37599499178065632</v>
+        <v>0.3821223699610294</v>
       </c>
       <c r="I3">
-        <v>0.41320650017592708</v>
+        <v>0.4253085086250326</v>
       </c>
       <c r="J3">
-        <v>0.38681871710250232</v>
+        <v>0.4037600626647871</v>
       </c>
       <c r="K3">
-        <v>0.3850244215170186</v>
+        <v>0.4021099365345735</v>
       </c>
       <c r="L3">
-        <v>0.4108828998947241</v>
+        <v>0.425630944755505</v>
       </c>
       <c r="M3">
-        <v>0.4366142197486505</v>
+        <v>0.4549698108840529</v>
       </c>
       <c r="N3">
-        <v>0.49771872656426253</v>
+        <v>0.5154417660020401</v>
       </c>
       <c r="O3">
-        <v>0.54574842915573052</v>
+        <v>0.5530980587630918</v>
       </c>
       <c r="P3">
-        <v>0.5411133009633835</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>18</v>
+        <v>0.5459661032523357</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_</t>
+        </is>
       </c>
       <c r="B4">
-        <v>3.9877792744118207E-2</v>
+        <v>0.04174701584896975</v>
       </c>
       <c r="C4">
-        <v>6.6605206785238708E-2</v>
+        <v>0.06419848535992394</v>
       </c>
       <c r="D4">
-        <v>0.1806190765714136</v>
+        <v>0.1697862106554446</v>
       </c>
       <c r="E4">
-        <v>0.18927711708605929</v>
+        <v>0.1775759463934417</v>
       </c>
       <c r="F4">
-        <v>0.35922505376808672</v>
+        <v>0.3432428877535393</v>
       </c>
       <c r="G4">
-        <v>0.3239980507935476</v>
+        <v>0.315797088899251</v>
       </c>
       <c r="H4">
-        <v>0.31379071830166638</v>
+        <v>0.3060232126559871</v>
       </c>
       <c r="I4">
-        <v>0.37935925044468571</v>
+        <v>0.3564725030807289</v>
       </c>
       <c r="J4">
-        <v>0.37043055361749011</v>
+        <v>0.3542801124487587</v>
       </c>
       <c r="K4">
-        <v>0.39527824236061587</v>
+        <v>0.3928904945154429</v>
       </c>
       <c r="L4">
-        <v>0.39739718396997542</v>
+        <v>0.3938987717170199</v>
       </c>
       <c r="M4">
-        <v>0.3956252701844854</v>
+        <v>0.3909434739532833</v>
       </c>
       <c r="N4">
-        <v>0.39004798159422882</v>
+        <v>0.3850538295457803</v>
       </c>
       <c r="O4">
-        <v>0.39770541469193538</v>
+        <v>0.3967009351653133</v>
       </c>
       <c r="P4">
-        <v>0.4234631280977133</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>19</v>
+        <v>0.4159925063204992</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B5">
-        <v>4.1640947311945418E-2</v>
+        <v>0.04239356207431472</v>
       </c>
       <c r="C5">
-        <v>0.1247869634604992</v>
+        <v>0.1358345324652967</v>
       </c>
       <c r="D5">
-        <v>0.1761174833146523</v>
+        <v>0.1738763280307555</v>
       </c>
       <c r="E5">
-        <v>0.46152968613657253</v>
+        <v>0.4612781786366424</v>
       </c>
       <c r="F5">
-        <v>0.32559788492718122</v>
+        <v>0.3250412069937172</v>
       </c>
       <c r="G5">
-        <v>0.37420205019957659</v>
+        <v>0.3681520295335126</v>
       </c>
       <c r="H5">
-        <v>0.36203542888160523</v>
+        <v>0.3635775175015543</v>
       </c>
       <c r="I5">
-        <v>0.36361301144848052</v>
+        <v>0.3580753830431493</v>
       </c>
       <c r="J5">
-        <v>0.32595565733384141</v>
+        <v>0.3272677293885392</v>
       </c>
       <c r="K5">
-        <v>0.32263567603310273</v>
+        <v>0.3250601114436255</v>
       </c>
       <c r="L5">
-        <v>0.31996387180807689</v>
+        <v>0.3271028748412628</v>
       </c>
       <c r="M5">
-        <v>0.33825920055866959</v>
+        <v>0.3478680583394126</v>
       </c>
       <c r="N5">
-        <v>0.37811835487324819</v>
+        <v>0.3920984834190143</v>
       </c>
       <c r="O5">
-        <v>0.41215421558546589</v>
+        <v>0.4266052800445939</v>
       </c>
       <c r="P5">
-        <v>0.45832469474627602</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>20</v>
+        <v>0.4702970154523893</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
+        </is>
       </c>
       <c r="B6">
-        <v>3.9300185573610757E-2</v>
+        <v>0.04223873852203387</v>
       </c>
       <c r="C6">
-        <v>0.1122622966508711</v>
+        <v>0.1226263851590011</v>
       </c>
       <c r="D6">
-        <v>0.16875468389047391</v>
+        <v>0.1635617044837593</v>
       </c>
       <c r="E6">
-        <v>0.43306886300846709</v>
+        <v>0.4246733149127465</v>
       </c>
       <c r="F6">
-        <v>0.2816154810485002</v>
+        <v>0.2716921856500748</v>
       </c>
       <c r="G6">
-        <v>0.27368504412281552</v>
+        <v>0.2624129977840659</v>
       </c>
       <c r="H6">
-        <v>0.27875493731569118</v>
+        <v>0.2547887087074374</v>
       </c>
       <c r="I6">
-        <v>0.26691575280830282</v>
+        <v>0.2546005714779216</v>
       </c>
       <c r="J6">
-        <v>0.25927859061364239</v>
+        <v>0.2523257990960845</v>
       </c>
       <c r="K6">
-        <v>0.25959199388945148</v>
+        <v>0.2494667570491737</v>
       </c>
       <c r="L6">
-        <v>0.27853634763345081</v>
+        <v>0.2669911266077576</v>
       </c>
       <c r="M6">
-        <v>0.29461882504774389</v>
+        <v>0.286698585568124</v>
       </c>
       <c r="N6">
-        <v>0.32413129827498771</v>
+        <v>0.3153548150669507</v>
       </c>
       <c r="O6">
-        <v>0.3317149333358832</v>
+        <v>0.3249407560508691</v>
       </c>
       <c r="P6">
-        <v>0.3706967208667869</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>21</v>
+        <v>0.3578427321909708</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_</t>
+        </is>
       </c>
       <c r="B7">
-        <v>3.8367168324321507E-2</v>
+        <v>0.04564740148382868</v>
       </c>
       <c r="C7">
-        <v>6.5567019159476589E-2</v>
+        <v>0.07353012749191674</v>
       </c>
       <c r="D7">
-        <v>0.17484002556266551</v>
+        <v>0.1834122046838182</v>
       </c>
       <c r="E7">
-        <v>0.21758337000771361</v>
+        <v>0.228559399665533</v>
       </c>
       <c r="F7">
-        <v>0.2895583978749644</v>
+        <v>0.3017130055527922</v>
       </c>
       <c r="G7">
-        <v>0.38576032320435749</v>
+        <v>0.4002487211042144</v>
       </c>
       <c r="H7">
-        <v>0.32795759572213662</v>
+        <v>0.3349153214281435</v>
       </c>
       <c r="I7">
-        <v>0.31169581080549191</v>
+        <v>0.3177706444936819</v>
       </c>
       <c r="J7">
-        <v>0.40962768304138558</v>
+        <v>0.4082974707340994</v>
       </c>
       <c r="K7">
-        <v>0.37719185625225271</v>
+        <v>0.3839842562857768</v>
       </c>
       <c r="L7">
-        <v>0.39770631759236708</v>
+        <v>0.4093381015838943</v>
       </c>
       <c r="M7">
-        <v>0.42691942051796072</v>
+        <v>0.4336515608034748</v>
       </c>
       <c r="N7">
-        <v>0.40373182312250938</v>
+        <v>0.4075635202385682</v>
       </c>
       <c r="O7">
-        <v>0.39657940303624462</v>
+        <v>0.3989366996201565</v>
       </c>
       <c r="P7">
-        <v>0.40253738988970572</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>22</v>
+        <v>0.4007725263533218</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
+        </is>
       </c>
       <c r="B8">
-        <v>3.8870308429818479E-2</v>
+        <v>0.03976775012989101</v>
       </c>
       <c r="C8">
-        <v>6.3423012168050491E-2</v>
+        <v>0.0619825775863721</v>
       </c>
       <c r="D8">
-        <v>0.17515675764433811</v>
+        <v>0.1650942481789164</v>
       </c>
       <c r="E8">
-        <v>0.2973330353121576</v>
+        <v>0.2968089706673592</v>
       </c>
       <c r="F8">
-        <v>0.3120123371010517</v>
+        <v>0.2977875912970573</v>
       </c>
       <c r="G8">
-        <v>0.30430022436064408</v>
+        <v>0.301275005951839</v>
       </c>
       <c r="H8">
-        <v>0.31232434088750832</v>
+        <v>0.3039868139218369</v>
       </c>
       <c r="I8">
-        <v>0.32673482797670311</v>
+        <v>0.3233770512071668</v>
       </c>
       <c r="J8">
-        <v>0.32321154302020177</v>
+        <v>0.3205148416890953</v>
       </c>
       <c r="K8">
-        <v>0.34341677618477179</v>
+        <v>0.3408905721491513</v>
       </c>
       <c r="L8">
-        <v>0.37469984452185001</v>
+        <v>0.3624086588759518</v>
       </c>
       <c r="M8">
-        <v>0.36786649169194569</v>
+        <v>0.3594368107842359</v>
       </c>
       <c r="N8">
-        <v>0.35252567972652271</v>
+        <v>0.3443747611822146</v>
       </c>
       <c r="O8">
-        <v>0.36714420024522959</v>
+        <v>0.3560357704553392</v>
       </c>
       <c r="P8">
-        <v>0.38317821487066189</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>23</v>
+        <v>0.3800728809808698</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
+        </is>
       </c>
       <c r="B9">
-        <v>3.7751763407746719E-2</v>
+        <v>0.03652986883185227</v>
       </c>
       <c r="C9">
-        <v>6.1697803748015881E-2</v>
+        <v>0.05823031216397123</v>
       </c>
       <c r="D9">
-        <v>0.15500156685821251</v>
+        <v>0.1564304163297987</v>
       </c>
       <c r="E9">
-        <v>0.26153018498229669</v>
+        <v>0.2590297529684507</v>
       </c>
       <c r="F9">
-        <v>0.26876096184589121</v>
+        <v>0.2697899475540978</v>
       </c>
       <c r="G9">
-        <v>0.25949087430244022</v>
+        <v>0.2581722006512554</v>
       </c>
       <c r="H9">
-        <v>0.26649674865111939</v>
+        <v>0.2529193721271513</v>
       </c>
       <c r="I9">
-        <v>0.26227847327631187</v>
+        <v>0.2604649687591896</v>
       </c>
       <c r="J9">
-        <v>0.25347031989747781</v>
+        <v>0.2524982330256135</v>
       </c>
       <c r="K9">
-        <v>0.24658047180048381</v>
+        <v>0.2447550939506252</v>
       </c>
       <c r="L9">
-        <v>0.27937544048137508</v>
+        <v>0.2714853074601899</v>
       </c>
       <c r="M9">
-        <v>0.2574351170186262</v>
+        <v>0.2535562725043113</v>
       </c>
       <c r="N9">
-        <v>0.24600974078349491</v>
+        <v>0.2443356353628868</v>
       </c>
       <c r="O9">
-        <v>0.2554476358419776</v>
+        <v>0.2535254974553028</v>
       </c>
       <c r="P9">
-        <v>0.28242433861832189</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>24</v>
+        <v>0.2763702470106977</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
+        </is>
       </c>
       <c r="B10">
-        <v>4.0861243794247097E-2</v>
+        <v>0.0401850507633475</v>
       </c>
       <c r="C10">
-        <v>6.4965795707995794E-2</v>
+        <v>0.06451801311481949</v>
       </c>
       <c r="D10">
-        <v>0.1624792801795823</v>
+        <v>0.1599553813970611</v>
       </c>
       <c r="E10">
-        <v>0.26807579860207348</v>
+        <v>0.2607118672994512</v>
       </c>
       <c r="F10">
-        <v>0.27822673464909081</v>
+        <v>0.2659229201589506</v>
       </c>
       <c r="G10">
-        <v>0.26636038767847969</v>
+        <v>0.2702357431826899</v>
       </c>
       <c r="H10">
-        <v>0.26594218636053701</v>
+        <v>0.2653719203769795</v>
       </c>
       <c r="I10">
-        <v>0.26261243905430381</v>
+        <v>0.2656232945816254</v>
       </c>
       <c r="J10">
-        <v>0.26049405667910031</v>
+        <v>0.2565160756598046</v>
       </c>
       <c r="K10">
-        <v>0.25014437952459728</v>
+        <v>0.2450925791713608</v>
       </c>
       <c r="L10">
-        <v>0.28540056392154428</v>
+        <v>0.2839215760617818</v>
       </c>
       <c r="M10">
-        <v>0.26919863893718893</v>
+        <v>0.2627963999045714</v>
       </c>
       <c r="N10">
-        <v>0.25954270627321591</v>
+        <v>0.2474535627719827</v>
       </c>
       <c r="O10">
-        <v>0.26558779376470187</v>
+        <v>0.2571140093968639</v>
       </c>
       <c r="P10">
-        <v>0.28911354384559329</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>25</v>
+        <v>0.2784705399254995</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B11">
-        <v>3.8742247353221522E-2</v>
+        <v>0.03922593793121484</v>
       </c>
       <c r="C11">
-        <v>6.0953274750715922E-2</v>
+        <v>0.06396984370076635</v>
       </c>
       <c r="D11">
-        <v>0.1608983514802162</v>
+        <v>0.1670854651232089</v>
       </c>
       <c r="E11">
-        <v>0.25901700253400828</v>
+        <v>0.2787370775670883</v>
       </c>
       <c r="F11">
-        <v>0.27287990164137532</v>
+        <v>0.2857753424197272</v>
       </c>
       <c r="G11">
-        <v>0.2641502585420657</v>
+        <v>0.2612047820972633</v>
       </c>
       <c r="H11">
-        <v>0.2670834384883603</v>
+        <v>0.2729815816714161</v>
       </c>
       <c r="I11">
-        <v>0.26977408511497453</v>
+        <v>0.2701818392410086</v>
       </c>
       <c r="J11">
-        <v>0.26601662728350223</v>
+        <v>0.2623128037076604</v>
       </c>
       <c r="K11">
-        <v>0.24742355472311131</v>
+        <v>0.2422911404280707</v>
       </c>
       <c r="L11">
-        <v>0.27210499966362112</v>
+        <v>0.2708732997191711</v>
       </c>
       <c r="M11">
-        <v>0.25223397080793891</v>
+        <v>0.252432030411266</v>
       </c>
       <c r="N11">
-        <v>0.24629064211119031</v>
+        <v>0.2436653093594777</v>
       </c>
       <c r="O11">
-        <v>0.25545753305177388</v>
+        <v>0.2561810415983424</v>
       </c>
       <c r="P11">
-        <v>0.26938438229085132</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>26</v>
+        <v>0.2710669877150534</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B12">
-        <v>4.5051599806409728E-2</v>
+        <v>0.04256528276193421</v>
       </c>
       <c r="C12">
-        <v>0.13259859582357311</v>
+        <v>0.1362916881376861</v>
       </c>
       <c r="D12">
-        <v>0.16130425212155661</v>
+        <v>0.1728722892940577</v>
       </c>
       <c r="E12">
-        <v>0.3999749746001553</v>
+        <v>0.4094854087606609</v>
       </c>
       <c r="F12">
-        <v>0.3387504750822079</v>
+        <v>0.3535258999053699</v>
       </c>
       <c r="G12">
-        <v>0.35384155984575272</v>
+        <v>0.3607680679800526</v>
       </c>
       <c r="H12">
-        <v>0.3308150480044173</v>
+        <v>0.337676498526142</v>
       </c>
       <c r="I12">
-        <v>0.3085602658909975</v>
+        <v>0.304778781504616</v>
       </c>
       <c r="J12">
-        <v>0.29414358309269689</v>
+        <v>0.292115596851576</v>
       </c>
       <c r="K12">
-        <v>0.29226306053546619</v>
+        <v>0.2879512478717307</v>
       </c>
       <c r="L12">
-        <v>0.29693924810071493</v>
+        <v>0.2933678139035074</v>
       </c>
       <c r="M12">
-        <v>0.31438796706094579</v>
+        <v>0.3130706302910846</v>
       </c>
       <c r="N12">
-        <v>0.35055609036954533</v>
+        <v>0.3486005259592077</v>
       </c>
       <c r="O12">
-        <v>0.38762541919406368</v>
+        <v>0.3853151573120642</v>
       </c>
       <c r="P12">
-        <v>0.45176010670714528</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>27</v>
+        <v>0.4466001436410882</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
+        </is>
       </c>
       <c r="B13">
-        <v>5.1437664434485858E-2</v>
+        <v>0.05322642830315513</v>
       </c>
       <c r="C13">
-        <v>0.20901005205997489</v>
+        <v>0.2121951081227109</v>
       </c>
       <c r="D13">
-        <v>0.27096146604667881</v>
+        <v>0.2759767924593327</v>
       </c>
       <c r="E13">
-        <v>0.38486425847513173</v>
+        <v>0.3867167806037138</v>
       </c>
       <c r="F13">
-        <v>0.50573634823296121</v>
+        <v>0.5041365460845322</v>
       </c>
       <c r="G13">
-        <v>0.48615829267177801</v>
+        <v>0.4763717648760747</v>
       </c>
       <c r="H13">
-        <v>0.55428328470813759</v>
+        <v>0.5511790204978742</v>
       </c>
       <c r="I13">
-        <v>0.53857996095185967</v>
+        <v>0.5347655314171949</v>
       </c>
       <c r="J13">
-        <v>0.50441999081490974</v>
+        <v>0.5159268377250056</v>
       </c>
       <c r="K13">
-        <v>0.4775611509712161</v>
+        <v>0.481766407826129</v>
       </c>
       <c r="L13">
-        <v>0.48577593752099729</v>
+        <v>0.4955998637366919</v>
       </c>
       <c r="M13">
-        <v>0.49951319957711482</v>
+        <v>0.5097570385038137</v>
       </c>
       <c r="N13">
-        <v>0.49765269000037787</v>
+        <v>0.5118630701557418</v>
       </c>
       <c r="O13">
-        <v>0.5078774321150632</v>
+        <v>0.5220565613991389</v>
       </c>
       <c r="P13">
-        <v>0.54367696850706571</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>28</v>
+        <v>0.5584586806784242</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+        </is>
       </c>
       <c r="B14">
-        <v>4.0317319278856283E-2</v>
+        <v>0.04115659675395007</v>
       </c>
       <c r="C14">
-        <v>7.0054328052734219E-2</v>
+        <v>0.06975238279574272</v>
       </c>
       <c r="D14">
-        <v>0.17194750570826139</v>
+        <v>0.1728598097078283</v>
       </c>
       <c r="E14">
-        <v>0.2057123197749299</v>
+        <v>0.2138411979817406</v>
       </c>
       <c r="F14">
-        <v>0.26945090351613599</v>
+        <v>0.2893750914344916</v>
       </c>
       <c r="G14">
-        <v>0.35711420042394632</v>
+        <v>0.3715746193618945</v>
       </c>
       <c r="H14">
-        <v>0.29534829694272902</v>
+        <v>0.3059386672332959</v>
       </c>
       <c r="I14">
-        <v>0.26667576955901079</v>
+        <v>0.2795530751696481</v>
       </c>
       <c r="J14">
-        <v>0.35467711859236611</v>
+        <v>0.3665783349860826</v>
       </c>
       <c r="K14">
-        <v>0.41093121586435682</v>
+        <v>0.4221182355741246</v>
       </c>
       <c r="L14">
-        <v>0.32201237749670453</v>
+        <v>0.3295785394338905</v>
       </c>
       <c r="M14">
-        <v>0.30951739393435551</v>
+        <v>0.3224031133523147</v>
       </c>
       <c r="N14">
-        <v>0.2891103455416566</v>
+        <v>0.2997555493586959</v>
       </c>
       <c r="O14">
-        <v>0.28551438746076713</v>
+        <v>0.2996907885588004</v>
       </c>
       <c r="P14">
-        <v>0.27977057577515352</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>29</v>
+        <v>0.2900974313510516</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B15">
-        <v>4.3180140838236E-2</v>
+        <v>0.04501907555915822</v>
       </c>
       <c r="C15">
-        <v>7.2159823495316855E-2</v>
+        <v>0.07479856121295549</v>
       </c>
       <c r="D15">
-        <v>0.17871837515830699</v>
+        <v>0.178170451428755</v>
       </c>
       <c r="E15">
-        <v>0.21486599522288879</v>
+        <v>0.2150232514046166</v>
       </c>
       <c r="F15">
-        <v>0.28752266845136992</v>
+        <v>0.2902880387907631</v>
       </c>
       <c r="G15">
-        <v>0.35734886976064129</v>
+        <v>0.3792363593779841</v>
       </c>
       <c r="H15">
-        <v>0.29863777406956338</v>
+        <v>0.3068490133076775</v>
       </c>
       <c r="I15">
-        <v>0.27325331591401558</v>
+        <v>0.2784406385786257</v>
       </c>
       <c r="J15">
-        <v>0.3640587234894167</v>
+        <v>0.3790638674538088</v>
       </c>
       <c r="K15">
-        <v>0.40545694766043439</v>
+        <v>0.4108053112201011</v>
       </c>
       <c r="L15">
-        <v>0.33123040660190839</v>
+        <v>0.3247926175500198</v>
       </c>
       <c r="M15">
-        <v>0.31719708811959713</v>
+        <v>0.3191626380447133</v>
       </c>
       <c r="N15">
-        <v>0.28783336971619039</v>
+        <v>0.2939425320865534</v>
       </c>
       <c r="O15">
-        <v>0.28388211967138688</v>
+        <v>0.2944973910606898</v>
       </c>
       <c r="P15">
-        <v>0.28508043564140251</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>30</v>
+        <v>0.2851771948836732</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
+        </is>
       </c>
       <c r="B16">
-        <v>3.9300754539805652E-2</v>
+        <v>0.04198764201915543</v>
       </c>
       <c r="C16">
-        <v>6.8641048273857114E-2</v>
+        <v>0.06780673298023737</v>
       </c>
       <c r="D16">
-        <v>0.17698761012593511</v>
+        <v>0.1682606073615877</v>
       </c>
       <c r="E16">
-        <v>0.2140824213142718</v>
+        <v>0.2067519521889673</v>
       </c>
       <c r="F16">
-        <v>0.28688692129137189</v>
+        <v>0.2681016603345417</v>
       </c>
       <c r="G16">
-        <v>0.3714751537311704</v>
+        <v>0.3601618990950864</v>
       </c>
       <c r="H16">
-        <v>0.30261612707789493</v>
+        <v>0.301473010875261</v>
       </c>
       <c r="I16">
-        <v>0.2764529426857229</v>
+        <v>0.2658593135085411</v>
       </c>
       <c r="J16">
-        <v>0.36056241379938903</v>
+        <v>0.3529371003323257</v>
       </c>
       <c r="K16">
-        <v>0.33347962307069029</v>
+        <v>0.3249077142243038</v>
       </c>
       <c r="L16">
-        <v>0.32505453193861572</v>
+        <v>0.316893472145883</v>
       </c>
       <c r="M16">
-        <v>0.31079755319202612</v>
+        <v>0.3062893264936263</v>
       </c>
       <c r="N16">
-        <v>0.28612253055276199</v>
+        <v>0.2763186454304307</v>
       </c>
       <c r="O16">
-        <v>0.28208545296129889</v>
+        <v>0.2740923900155002</v>
       </c>
       <c r="P16">
-        <v>0.2720111272011132</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>31</v>
+        <v>0.2740510259329297</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+        </is>
       </c>
       <c r="B17">
-        <v>3.8395251435673683E-2</v>
+        <v>0.03869027236601501</v>
       </c>
       <c r="C17">
-        <v>6.7496433179274395E-2</v>
+        <v>0.07011588415315817</v>
       </c>
       <c r="D17">
-        <v>0.1731755682833486</v>
+        <v>0.1745367320525192</v>
       </c>
       <c r="E17">
-        <v>0.21355338357655829</v>
+        <v>0.2085823933320769</v>
       </c>
       <c r="F17">
-        <v>0.27714199380270021</v>
+        <v>0.2673207987310122</v>
       </c>
       <c r="G17">
-        <v>0.35948483871163911</v>
+        <v>0.3577051848628112</v>
       </c>
       <c r="H17">
-        <v>0.30165053376798828</v>
+        <v>0.2946777382968144</v>
       </c>
       <c r="I17">
-        <v>0.27245342183207799</v>
+        <v>0.2638843046805847</v>
       </c>
       <c r="J17">
-        <v>0.36714608692252088</v>
+        <v>0.3560615054985022</v>
       </c>
       <c r="K17">
-        <v>0.3693000837196907</v>
+        <v>0.3561193145028001</v>
       </c>
       <c r="L17">
-        <v>0.33957788463517702</v>
+        <v>0.3313400684975948</v>
       </c>
       <c r="M17">
-        <v>0.32169313958934742</v>
+        <v>0.3177289722488921</v>
       </c>
       <c r="N17">
-        <v>0.29657520641930168</v>
+        <v>0.3003966191676157</v>
       </c>
       <c r="O17">
-        <v>0.29026863962953392</v>
+        <v>0.2968666115770855</v>
       </c>
       <c r="P17">
-        <v>0.28403806791879549</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>32</v>
+        <v>0.2915674129934955</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B18">
-        <v>4.4714175438185913E-2</v>
+        <v>0.04316359209887288</v>
       </c>
       <c r="C18">
-        <v>0.13549819253894579</v>
+        <v>0.1378703546360111</v>
       </c>
       <c r="D18">
-        <v>0.16727581687032711</v>
+        <v>0.1774012863044894</v>
       </c>
       <c r="E18">
-        <v>0.43390030104891042</v>
+        <v>0.4349065045604881</v>
       </c>
       <c r="F18">
-        <v>0.32812972644822952</v>
+        <v>0.3189266056179478</v>
       </c>
       <c r="G18">
-        <v>0.35730704717040801</v>
+        <v>0.3554979010068385</v>
       </c>
       <c r="H18">
-        <v>0.3385641462258358</v>
+        <v>0.334522071661597</v>
       </c>
       <c r="I18">
-        <v>0.33376487864410248</v>
+        <v>0.3324707833883523</v>
       </c>
       <c r="J18">
-        <v>0.30487505077166333</v>
+        <v>0.3053734886072024</v>
       </c>
       <c r="K18">
-        <v>0.29638885623418731</v>
+        <v>0.3010038247275956</v>
       </c>
       <c r="L18">
-        <v>0.30563163469795618</v>
+        <v>0.3079658660310806</v>
       </c>
       <c r="M18">
-        <v>0.32233166195172253</v>
+        <v>0.3217296587195967</v>
       </c>
       <c r="N18">
-        <v>0.36929422245842408</v>
+        <v>0.3694686693905328</v>
       </c>
       <c r="O18">
-        <v>0.40903096799935329</v>
+        <v>0.4103541622679898</v>
       </c>
       <c r="P18">
-        <v>0.44517503084412108</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>33</v>
+        <v>0.4510578555953885</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
+        </is>
       </c>
       <c r="B19">
-        <v>4.4286658298576177E-2</v>
+        <v>0.04302431015676204</v>
       </c>
       <c r="C19">
-        <v>0.13306442052034359</v>
+        <v>0.1295696830297616</v>
       </c>
       <c r="D19">
-        <v>0.1891203866542131</v>
+        <v>0.1844766799669996</v>
       </c>
       <c r="E19">
-        <v>0.42135631374002791</v>
+        <v>0.4352880343932952</v>
       </c>
       <c r="F19">
-        <v>0.29317905109392889</v>
+        <v>0.2902268086242805</v>
       </c>
       <c r="G19">
-        <v>0.27167909425203401</v>
+        <v>0.2801534605543784</v>
       </c>
       <c r="H19">
-        <v>0.26831930718839969</v>
+        <v>0.2717039642664086</v>
       </c>
       <c r="I19">
-        <v>0.24969340856416011</v>
+        <v>0.2538813161926359</v>
       </c>
       <c r="J19">
-        <v>0.24063034331162891</v>
+        <v>0.2475759429187336</v>
       </c>
       <c r="K19">
-        <v>0.2489368966930256</v>
+        <v>0.2545718579962797</v>
       </c>
       <c r="L19">
-        <v>0.2754505079506312</v>
+        <v>0.276233775663222</v>
       </c>
       <c r="M19">
-        <v>0.29720750994711009</v>
+        <v>0.2960438733593971</v>
       </c>
       <c r="N19">
-        <v>0.33563747125740961</v>
+        <v>0.3317607414392896</v>
       </c>
       <c r="O19">
-        <v>0.33714749512768882</v>
+        <v>0.3381467845672324</v>
       </c>
       <c r="P19">
-        <v>0.35925291280290422</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>34</v>
+        <v>0.3644970762190642</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+        </is>
       </c>
       <c r="B20">
-        <v>4.2437695586772461E-2</v>
+        <v>0.04109496151105804</v>
       </c>
       <c r="C20">
-        <v>0.10226389371958219</v>
+        <v>0.0958436872106963</v>
       </c>
       <c r="D20">
-        <v>0.20865034345816541</v>
+        <v>0.2124932073090348</v>
       </c>
       <c r="E20">
-        <v>0.28131123521554879</v>
+        <v>0.2856690854116579</v>
       </c>
       <c r="F20">
-        <v>0.22748441887650189</v>
+        <v>0.2398939657363673</v>
       </c>
       <c r="G20">
-        <v>0.31030958877891779</v>
+        <v>0.3278749209918272</v>
       </c>
       <c r="H20">
-        <v>0.25270845242704981</v>
+        <v>0.2677259656275432</v>
       </c>
       <c r="I20">
-        <v>0.24364313469317919</v>
+        <v>0.2510245224334115</v>
       </c>
       <c r="J20">
-        <v>0.2307127297723251</v>
+        <v>0.2360431247944298</v>
       </c>
       <c r="K20">
-        <v>0.23074256796986739</v>
+        <v>0.2388654050970878</v>
       </c>
       <c r="L20">
-        <v>0.24916396043341801</v>
+        <v>0.2571392815914986</v>
       </c>
       <c r="M20">
-        <v>0.29022879263348389</v>
+        <v>0.2959763709693907</v>
       </c>
       <c r="N20">
-        <v>0.26202139024777982</v>
+        <v>0.2669356537015624</v>
       </c>
       <c r="O20">
-        <v>0.2841390930477008</v>
+        <v>0.2898067722042237</v>
       </c>
       <c r="P20">
-        <v>0.30303298337180262</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>35</v>
+        <v>0.3144747339607464</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B21">
-        <v>6.3038233788616282E-2</v>
+        <v>0.06165924729854524</v>
       </c>
       <c r="C21">
-        <v>0.1007397561248118</v>
+        <v>0.1020424741433353</v>
       </c>
       <c r="D21">
-        <v>0.45904672379884759</v>
+        <v>0.4730261008971418</v>
       </c>
       <c r="E21">
-        <v>0.32535618970539559</v>
+        <v>0.3448547362150225</v>
       </c>
       <c r="F21">
-        <v>0.33529530451376771</v>
+        <v>0.3449109648777063</v>
       </c>
       <c r="G21">
-        <v>0.34905236893406782</v>
+        <v>0.3551632036505384</v>
       </c>
       <c r="H21">
-        <v>0.40919905258901762</v>
+        <v>0.4119218018128617</v>
       </c>
       <c r="I21">
-        <v>0.43407419617016518</v>
+        <v>0.4536300191980963</v>
       </c>
       <c r="J21">
-        <v>0.40712930620957888</v>
+        <v>0.4087232213225347</v>
       </c>
       <c r="K21">
-        <v>0.41048717424628489</v>
+        <v>0.4151733944082412</v>
       </c>
       <c r="L21">
-        <v>0.41840421123372262</v>
+        <v>0.4222606353918158</v>
       </c>
       <c r="M21">
-        <v>0.45847099751492459</v>
+        <v>0.4585925746740792</v>
       </c>
       <c r="N21">
-        <v>0.51830721282777414</v>
+        <v>0.5130791625835267</v>
       </c>
       <c r="O21">
-        <v>0.56247768723938041</v>
+        <v>0.558283842434431</v>
       </c>
       <c r="P21">
-        <v>0.57264626835003729</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>36</v>
+        <v>0.5660207990045247</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B22">
-        <v>5.893719934674449E-2</v>
+        <v>0.06267963026293685</v>
       </c>
       <c r="C22">
-        <v>0.1001265303103247</v>
+        <v>0.1039261732416468</v>
       </c>
       <c r="D22">
-        <v>0.45442469264539731</v>
+        <v>0.465274365787498</v>
       </c>
       <c r="E22">
-        <v>0.31874334120266301</v>
+        <v>0.3245379026990681</v>
       </c>
       <c r="F22">
-        <v>0.31843685431546292</v>
+        <v>0.3289095910332301</v>
       </c>
       <c r="G22">
-        <v>0.34231063698069047</v>
+        <v>0.3466101063454723</v>
       </c>
       <c r="H22">
-        <v>0.41689211131537912</v>
+        <v>0.4215363934574069</v>
       </c>
       <c r="I22">
-        <v>0.45779249420959622</v>
+        <v>0.4705739409802746</v>
       </c>
       <c r="J22">
-        <v>0.4228644457354333</v>
+        <v>0.4331666223979143</v>
       </c>
       <c r="K22">
-        <v>0.42884734928507218</v>
+        <v>0.4454418786746462</v>
       </c>
       <c r="L22">
-        <v>0.45465787045265138</v>
+        <v>0.4736269182528977</v>
       </c>
       <c r="M22">
-        <v>0.48435894679542618</v>
+        <v>0.5015813825524974</v>
       </c>
       <c r="N22">
-        <v>0.52481502602627594</v>
+        <v>0.5427699932191442</v>
       </c>
       <c r="O22">
-        <v>0.54571080541595229</v>
+        <v>0.5653417999413026</v>
       </c>
       <c r="P22">
-        <v>0.56412697245038845</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>37</v>
+        <v>0.5860202396173591</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B23">
-        <v>4.8571668797937333E-2</v>
+        <v>0.04505083777502146</v>
       </c>
       <c r="C23">
-        <v>0.2125822072636947</v>
+        <v>0.2128460637855387</v>
       </c>
       <c r="D23">
-        <v>0.1930908679019373</v>
+        <v>0.1761055979689771</v>
       </c>
       <c r="E23">
-        <v>0.21138889663692051</v>
+        <v>0.204437335232499</v>
       </c>
       <c r="F23">
-        <v>0.25757943621107071</v>
+        <v>0.2510729099709016</v>
       </c>
       <c r="G23">
-        <v>0.25628764386186209</v>
+        <v>0.2492951426416379</v>
       </c>
       <c r="H23">
-        <v>0.27070984159054229</v>
+        <v>0.2650598926047852</v>
       </c>
       <c r="I23">
-        <v>0.3005753087943478</v>
+        <v>0.2935949943918194</v>
       </c>
       <c r="J23">
-        <v>0.3012527757831916</v>
+        <v>0.2982629961163693</v>
       </c>
       <c r="K23">
-        <v>0.33895186494322749</v>
+        <v>0.342504728757715</v>
       </c>
       <c r="L23">
-        <v>0.36903143365722318</v>
+        <v>0.3757420421604451</v>
       </c>
       <c r="M23">
-        <v>0.42889571493564072</v>
+        <v>0.4357646926090479</v>
       </c>
       <c r="N23">
-        <v>0.45418580488620619</v>
+        <v>0.4600218898258338</v>
       </c>
       <c r="O23">
-        <v>0.48226217917062841</v>
+        <v>0.4919302331200235</v>
       </c>
       <c r="P23">
-        <v>0.53009274186573241</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>38</v>
+        <v>0.5359141175397575</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>adj_red_c(950,20,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B24">
-        <v>0.15494119015872049</v>
+        <v>0.1579540895918941</v>
       </c>
       <c r="C24">
-        <v>0.13336889122269241</v>
+        <v>0.1353666226516572</v>
       </c>
       <c r="D24">
-        <v>0.16666462855985209</v>
+        <v>0.1765178073307431</v>
       </c>
       <c r="E24">
-        <v>0.2489522139580323</v>
+        <v>0.2577407261703716</v>
       </c>
       <c r="F24">
-        <v>0.37858327779799061</v>
+        <v>0.385726349256477</v>
       </c>
       <c r="G24">
-        <v>0.59692198882910397</v>
+        <v>0.6105225624586138</v>
       </c>
       <c r="H24">
-        <v>0.61316530346780396</v>
+        <v>0.6241916651076647</v>
       </c>
       <c r="I24">
-        <v>0.67976163151758406</v>
+        <v>0.6934543070802517</v>
       </c>
       <c r="J24">
-        <v>0.80310587729012317</v>
+        <v>0.8120487402058589</v>
       </c>
       <c r="K24">
-        <v>0.99545866268644723</v>
+        <v>1.008958228882128</v>
       </c>
       <c r="L24">
-        <v>1.02689965280339</v>
+        <v>1.049274923210439</v>
       </c>
       <c r="M24">
-        <v>1.0994908209286489</v>
+        <v>1.121577201357097</v>
       </c>
       <c r="N24">
-        <v>1.195931907931951</v>
+        <v>1.231050830125415</v>
       </c>
       <c r="O24">
-        <v>1.3100666652321951</v>
+        <v>1.330567408951456</v>
       </c>
       <c r="P24">
-        <v>1.4279274721642921</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>39</v>
+        <v>1.439471443309416</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>adj_red_c(950,20,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B25">
-        <v>0.4612268834171066</v>
+        <v>0.4549330591330902</v>
       </c>
       <c r="C25">
-        <v>0.44057400342474778</v>
+        <v>0.4324093107559615</v>
       </c>
       <c r="D25">
-        <v>0.46855910877673979</v>
+        <v>0.4631005065975493</v>
       </c>
       <c r="E25">
-        <v>0.50497392077790126</v>
+        <v>0.503216455558521</v>
       </c>
       <c r="F25">
-        <v>0.67122772787620033</v>
+        <v>0.6618735724794155</v>
       </c>
       <c r="G25">
-        <v>0.76682863481618346</v>
+        <v>0.7557095614557708</v>
       </c>
       <c r="H25">
-        <v>0.83007428637558656</v>
+        <v>0.8179060250498315</v>
       </c>
       <c r="I25">
-        <v>0.85784692159471421</v>
+        <v>0.8493556138074505</v>
       </c>
       <c r="J25">
-        <v>0.89643394077238803</v>
+        <v>0.8960251143300175</v>
       </c>
       <c r="K25">
-        <v>1.025016359040686</v>
+        <v>1.033459164549201</v>
       </c>
       <c r="L25">
-        <v>1.095749312961426</v>
+        <v>1.108378539221623</v>
       </c>
       <c r="M25">
-        <v>1.2471298759733609</v>
+        <v>1.260002993206105</v>
       </c>
       <c r="N25">
-        <v>1.367084366316224</v>
+        <v>1.387834343541871</v>
       </c>
       <c r="O25">
-        <v>1.442402067507881</v>
+        <v>1.462302307108179</v>
       </c>
       <c r="P25">
-        <v>1.4968722227518481</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>40</v>
+        <v>1.500067107220984</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>adj_red_c(950,750,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B26">
-        <v>0.1472276022977303</v>
+        <v>0.1449490457115274</v>
       </c>
       <c r="C26">
-        <v>0.16947958064683999</v>
+        <v>0.1657337120714573</v>
       </c>
       <c r="D26">
-        <v>0.1398076198620446</v>
+        <v>0.1424283114349797</v>
       </c>
       <c r="E26">
-        <v>0.13506359433898099</v>
+        <v>0.1361005591527559</v>
       </c>
       <c r="F26">
-        <v>0.26181595869154689</v>
+        <v>0.2640384996949577</v>
       </c>
       <c r="G26">
-        <v>0.25603965509842902</v>
+        <v>0.2627595750630973</v>
       </c>
       <c r="H26">
-        <v>0.2787708150000664</v>
+        <v>0.2840299976735355</v>
       </c>
       <c r="I26">
-        <v>0.35867688041656592</v>
+        <v>0.3592951270780057</v>
       </c>
       <c r="J26">
-        <v>0.38050534377730028</v>
+        <v>0.381162371129824</v>
       </c>
       <c r="K26">
-        <v>0.44741480919239363</v>
+        <v>0.4396277223428823</v>
       </c>
       <c r="L26">
-        <v>0.49999114375222692</v>
+        <v>0.4908239396257388</v>
       </c>
       <c r="M26">
-        <v>0.5427897866642547</v>
+        <v>0.5395778741339956</v>
       </c>
       <c r="N26">
-        <v>0.60217148795305164</v>
+        <v>0.5979552736184721</v>
       </c>
       <c r="O26">
-        <v>0.69263979181763191</v>
+        <v>0.6833235170778074</v>
       </c>
       <c r="P26">
-        <v>0.76137994475269921</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>41</v>
+        <v>0.7539812645112663</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>adj_red_c(950,750,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B27">
-        <v>0.16971880236769149</v>
+        <v>0.1717882625908206</v>
       </c>
       <c r="C27">
-        <v>0.1442156433163492</v>
+        <v>0.1430735270839106</v>
       </c>
       <c r="D27">
-        <v>0.17386227475298999</v>
+        <v>0.1651127534968155</v>
       </c>
       <c r="E27">
-        <v>0.15007878763176979</v>
+        <v>0.1582876267676291</v>
       </c>
       <c r="F27">
-        <v>0.29993514632287033</v>
+        <v>0.301282546720369</v>
       </c>
       <c r="G27">
-        <v>0.3516501574213205</v>
+        <v>0.3534522422322015</v>
       </c>
       <c r="H27">
-        <v>0.42834092627272352</v>
+        <v>0.4311043069110113</v>
       </c>
       <c r="I27">
-        <v>0.59044778946092891</v>
+        <v>0.5868374161687905</v>
       </c>
       <c r="J27">
-        <v>0.64029614280703506</v>
+        <v>0.64392918842961</v>
       </c>
       <c r="K27">
-        <v>0.66361008868775528</v>
+        <v>0.6684037161994251</v>
       </c>
       <c r="L27">
-        <v>0.64353732637405403</v>
+        <v>0.651055012746885</v>
       </c>
       <c r="M27">
-        <v>0.65958637464100589</v>
+        <v>0.6681792429563167</v>
       </c>
       <c r="N27">
-        <v>0.69996598655646924</v>
+        <v>0.705329907801415</v>
       </c>
       <c r="O27">
-        <v>0.79009912128232052</v>
+        <v>0.7990666565977538</v>
       </c>
       <c r="P27">
-        <v>0.85523234070436382</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>42</v>
+        <v>0.861240843421337</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
+        </is>
       </c>
       <c r="B28">
-        <v>4.1160008939857287E-2</v>
+        <v>0.04057948458472652</v>
       </c>
       <c r="C28">
-        <v>0.16331288913434761</v>
+        <v>0.1618204323733578</v>
       </c>
       <c r="D28">
-        <v>0.19429686595745899</v>
+        <v>0.1969849765365562</v>
       </c>
       <c r="E28">
-        <v>0.1942597916194507</v>
+        <v>0.1971973976528395</v>
       </c>
       <c r="F28">
-        <v>0.23080111826430191</v>
+        <v>0.2356489192539993</v>
       </c>
       <c r="G28">
-        <v>0.22245352665268109</v>
+        <v>0.2228210113989856</v>
       </c>
       <c r="H28">
-        <v>0.35435633409607492</v>
+        <v>0.3406532440551215</v>
       </c>
       <c r="I28">
-        <v>0.4288119967048124</v>
+        <v>0.428778824730799</v>
       </c>
       <c r="J28">
-        <v>0.46257627533733331</v>
+        <v>0.4698527941911672</v>
       </c>
       <c r="K28">
-        <v>0.44530884164806639</v>
+        <v>0.4364028088605478</v>
       </c>
       <c r="L28">
-        <v>0.44872577222821458</v>
+        <v>0.4475970973977</v>
       </c>
       <c r="M28">
-        <v>0.53189110114822635</v>
+        <v>0.5355171151140157</v>
       </c>
       <c r="N28">
-        <v>0.6529042088898469</v>
+        <v>0.6594066472158383</v>
       </c>
       <c r="O28">
-        <v>0.72887924703275508</v>
+        <v>0.7326123668782587</v>
       </c>
       <c r="P28">
-        <v>0.82168968839734469</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>43</v>
+        <v>0.8304017733566105</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
+        </is>
       </c>
       <c r="B29">
-        <v>4.5404770460997362E-2</v>
+        <v>0.04461081502281936</v>
       </c>
       <c r="C29">
-        <v>0.18135592948374021</v>
+        <v>0.1792971141027531</v>
       </c>
       <c r="D29">
-        <v>0.2130957215375249</v>
+        <v>0.2112834136046649</v>
       </c>
       <c r="E29">
-        <v>0.2120842649166351</v>
+        <v>0.2088507904920523</v>
       </c>
       <c r="F29">
-        <v>0.21046090345421231</v>
+        <v>0.2114405898289305</v>
       </c>
       <c r="G29">
-        <v>0.237412627337099</v>
+        <v>0.239739277175272</v>
       </c>
       <c r="H29">
-        <v>0.36211520020929011</v>
+        <v>0.3612376113069862</v>
       </c>
       <c r="I29">
-        <v>0.52755134289104066</v>
+        <v>0.5051471718760651</v>
       </c>
       <c r="J29">
-        <v>0.49823615067205829</v>
+        <v>0.4984190961905731</v>
       </c>
       <c r="K29">
-        <v>0.46313119573779338</v>
+        <v>0.4640885662436787</v>
       </c>
       <c r="L29">
-        <v>0.4554703891489274</v>
+        <v>0.4593256379687709</v>
       </c>
       <c r="M29">
-        <v>0.49020429039517383</v>
+        <v>0.4879610884339858</v>
       </c>
       <c r="N29">
-        <v>0.56564060547043071</v>
+        <v>0.5664910396228786</v>
       </c>
       <c r="O29">
-        <v>0.67291219493228105</v>
+        <v>0.6680424616064409</v>
       </c>
       <c r="P29">
-        <v>0.74745355269455982</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>44</v>
+        <v>0.7467623991321028</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
+        </is>
       </c>
       <c r="B30">
-        <v>4.278936104966477E-2</v>
+        <v>0.04071248360774892</v>
       </c>
       <c r="C30">
-        <v>0.19579447511991799</v>
+        <v>0.1910677478584012</v>
       </c>
       <c r="D30">
-        <v>0.18630600418782331</v>
+        <v>0.1795028869907874</v>
       </c>
       <c r="E30">
-        <v>0.18557360615033011</v>
+        <v>0.1768892074159163</v>
       </c>
       <c r="F30">
-        <v>0.2514308760503528</v>
+        <v>0.2561325598332798</v>
       </c>
       <c r="G30">
-        <v>0.26664367658686522</v>
+        <v>0.2715673581461773</v>
       </c>
       <c r="H30">
-        <v>0.34690635513610651</v>
+        <v>0.3553515786396781</v>
       </c>
       <c r="I30">
-        <v>0.55889617367794397</v>
+        <v>0.5675965785528275</v>
       </c>
       <c r="J30">
-        <v>0.46367342773009068</v>
+        <v>0.4749450158737274</v>
       </c>
       <c r="K30">
-        <v>0.46886958902552472</v>
+        <v>0.4739402753245354</v>
       </c>
       <c r="L30">
-        <v>0.52252085494434686</v>
+        <v>0.5189355460817691</v>
       </c>
       <c r="M30">
-        <v>0.61080199543024005</v>
+        <v>0.6022955501931924</v>
       </c>
       <c r="N30">
-        <v>0.68569783878645119</v>
+        <v>0.6732595877671608</v>
       </c>
       <c r="O30">
-        <v>0.75394424687394768</v>
+        <v>0.7471460569946691</v>
       </c>
       <c r="P30">
-        <v>0.85182867684285146</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>45</v>
+        <v>0.8496031635239492</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B31">
-        <v>3.9018934320186778E-2</v>
+        <v>0.04436686298211666</v>
       </c>
       <c r="C31">
-        <v>0.188209066619453</v>
+        <v>0.1917608507251619</v>
       </c>
       <c r="D31">
-        <v>0.17934630899412579</v>
+        <v>0.183232280578652</v>
       </c>
       <c r="E31">
-        <v>0.16275796444108451</v>
+        <v>0.1676654594547975</v>
       </c>
       <c r="F31">
-        <v>0.22447798983210229</v>
+        <v>0.2255838948485056</v>
       </c>
       <c r="G31">
-        <v>0.22595690621476511</v>
+        <v>0.2304391221897258</v>
       </c>
       <c r="H31">
-        <v>0.24390045835006149</v>
+        <v>0.24859377770385</v>
       </c>
       <c r="I31">
-        <v>0.40746690938805369</v>
+        <v>0.4222297245427102</v>
       </c>
       <c r="J31">
-        <v>0.3446899522710215</v>
+        <v>0.3498787581249749</v>
       </c>
       <c r="K31">
-        <v>0.31319732262408118</v>
+        <v>0.3102612824454967</v>
       </c>
       <c r="L31">
-        <v>0.30422870241500483</v>
+        <v>0.298507082558955</v>
       </c>
       <c r="M31">
-        <v>0.34876370090513381</v>
+        <v>0.3448657481621842</v>
       </c>
       <c r="N31">
-        <v>0.37066840538808138</v>
+        <v>0.3643715471868081</v>
       </c>
       <c r="O31">
-        <v>0.42354409244737518</v>
+        <v>0.4092163652660056</v>
       </c>
       <c r="P31">
-        <v>0.45200029961171739</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>46</v>
+        <v>0.4361528838981067</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
+        </is>
       </c>
       <c r="B32">
-        <v>4.2821107740244939E-2</v>
+        <v>0.04172277674150839</v>
       </c>
       <c r="C32">
-        <v>0.17597464607853461</v>
+        <v>0.1718774683018272</v>
       </c>
       <c r="D32">
-        <v>0.20909485470426939</v>
+        <v>0.2055656442811605</v>
       </c>
       <c r="E32">
-        <v>0.20331512273547339</v>
+        <v>0.1977798721315083</v>
       </c>
       <c r="F32">
-        <v>0.20130757446468889</v>
+        <v>0.1956614350131901</v>
       </c>
       <c r="G32">
-        <v>0.21484326791256789</v>
+        <v>0.2103430787884324</v>
       </c>
       <c r="H32">
-        <v>0.2978808391312926</v>
+        <v>0.2870379025728904</v>
       </c>
       <c r="I32">
-        <v>0.40731336990764128</v>
+        <v>0.4060741522022123</v>
       </c>
       <c r="J32">
-        <v>0.38462510175928921</v>
+        <v>0.3891065487725651</v>
       </c>
       <c r="K32">
-        <v>0.35684233630327</v>
+        <v>0.3559963416638259</v>
       </c>
       <c r="L32">
-        <v>0.31006605911129193</v>
+        <v>0.3063821618093588</v>
       </c>
       <c r="M32">
-        <v>0.31659888230642802</v>
+        <v>0.3113717399937131</v>
       </c>
       <c r="N32">
-        <v>0.36440598899133059</v>
+        <v>0.352134731140348</v>
       </c>
       <c r="O32">
-        <v>0.41179070553558328</v>
+        <v>0.4065446626229785</v>
       </c>
       <c r="P32">
-        <v>0.44350836938896498</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>47</v>
+        <v>0.4316691250039352</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
+        </is>
       </c>
       <c r="B33">
-        <v>4.6489636250847018E-2</v>
+        <v>0.04282491829682174</v>
       </c>
       <c r="C33">
-        <v>0.1788762240721499</v>
+        <v>0.1759380294119303</v>
       </c>
       <c r="D33">
-        <v>0.21098910901025941</v>
+        <v>0.2070095182790684</v>
       </c>
       <c r="E33">
-        <v>0.20086991705739571</v>
+        <v>0.1991419696498896</v>
       </c>
       <c r="F33">
-        <v>0.19748508542199711</v>
+        <v>0.1962786542403793</v>
       </c>
       <c r="G33">
-        <v>0.21060736884180239</v>
+        <v>0.2075095320005881</v>
       </c>
       <c r="H33">
-        <v>0.29851162307565898</v>
+        <v>0.2858517031641721</v>
       </c>
       <c r="I33">
-        <v>0.39384368379829099</v>
+        <v>0.3938268336022812</v>
       </c>
       <c r="J33">
-        <v>0.37892974387245421</v>
+        <v>0.382016296544759</v>
       </c>
       <c r="K33">
-        <v>0.33557105227049522</v>
+        <v>0.3285440057526851</v>
       </c>
       <c r="L33">
-        <v>0.29174470369539662</v>
+        <v>0.2918870528085471</v>
       </c>
       <c r="M33">
-        <v>0.28877816511415128</v>
+        <v>0.2933769333478792</v>
       </c>
       <c r="N33">
-        <v>0.33177542663641152</v>
+        <v>0.3326445324194995</v>
       </c>
       <c r="O33">
-        <v>0.37666494995327682</v>
+        <v>0.3715267439103312</v>
       </c>
       <c r="P33">
-        <v>0.39775328013006211</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>48</v>
+        <v>0.3933256028501858</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
+        </is>
       </c>
       <c r="B34">
-        <v>4.2330865649998287E-2</v>
+        <v>0.04323031608997881</v>
       </c>
       <c r="C34">
-        <v>0.17556032468975699</v>
+        <v>0.1725896086472783</v>
       </c>
       <c r="D34">
-        <v>0.20668921186899841</v>
+        <v>0.2054811432623284</v>
       </c>
       <c r="E34">
-        <v>0.20070000368886451</v>
+        <v>0.1984654434491969</v>
       </c>
       <c r="F34">
-        <v>0.2011680070998326</v>
+        <v>0.1933089074114444</v>
       </c>
       <c r="G34">
-        <v>0.211318058337402</v>
+        <v>0.1997128901097538</v>
       </c>
       <c r="H34">
-        <v>0.28585242675865918</v>
+        <v>0.2784015922771361</v>
       </c>
       <c r="I34">
-        <v>0.39914953511162321</v>
+        <v>0.3986812196206064</v>
       </c>
       <c r="J34">
-        <v>0.38837840142199709</v>
+        <v>0.3864546669592043</v>
       </c>
       <c r="K34">
-        <v>0.33520140067723381</v>
+        <v>0.3313415759482878</v>
       </c>
       <c r="L34">
-        <v>0.30431538265107799</v>
+        <v>0.2971851887094664</v>
       </c>
       <c r="M34">
-        <v>0.29393264170341071</v>
+        <v>0.2947141504589053</v>
       </c>
       <c r="N34">
-        <v>0.34015291306948631</v>
+        <v>0.3470825004563489</v>
       </c>
       <c r="O34">
-        <v>0.39165655112525571</v>
+        <v>0.3780087043952886</v>
       </c>
       <c r="P34">
-        <v>0.40739646435257049</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>49</v>
+        <v>0.4063027047820256</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
+        </is>
       </c>
       <c r="B35">
-        <v>4.9965658358968691E-2</v>
+        <v>0.04527389952319913</v>
       </c>
       <c r="C35">
-        <v>0.17863012251529009</v>
+        <v>0.1763058902150497</v>
       </c>
       <c r="D35">
-        <v>0.2141223514762457</v>
+        <v>0.2136019692511651</v>
       </c>
       <c r="E35">
-        <v>0.20794722297458321</v>
+        <v>0.2019415204175856</v>
       </c>
       <c r="F35">
-        <v>0.20887130097808729</v>
+        <v>0.2009334837947678</v>
       </c>
       <c r="G35">
-        <v>0.21340024316078501</v>
+        <v>0.2101041847141298</v>
       </c>
       <c r="H35">
-        <v>0.28723283530381161</v>
+        <v>0.2951607597196911</v>
       </c>
       <c r="I35">
-        <v>0.39747103516513271</v>
+        <v>0.4080311130731266</v>
       </c>
       <c r="J35">
-        <v>0.40109852959462933</v>
+        <v>0.4063734579382028</v>
       </c>
       <c r="K35">
-        <v>0.3479002809319961</v>
+        <v>0.3523975252478285</v>
       </c>
       <c r="L35">
-        <v>0.30957528201001999</v>
+        <v>0.3135723152882788</v>
       </c>
       <c r="M35">
-        <v>0.29684309742059578</v>
+        <v>0.2962620653303433</v>
       </c>
       <c r="N35">
-        <v>0.33240099085761882</v>
+        <v>0.331795445061404</v>
       </c>
       <c r="O35">
-        <v>0.37840318333492129</v>
+        <v>0.3778579781986472</v>
       </c>
       <c r="P35">
-        <v>0.38300866236787251</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>50</v>
+        <v>0.382854983629071</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+        </is>
       </c>
       <c r="B36">
-        <v>4.39685891084933E-2</v>
+        <v>0.0457456886195533</v>
       </c>
       <c r="C36">
-        <v>0.17279557423812511</v>
+        <v>0.1812680454897064</v>
       </c>
       <c r="D36">
-        <v>0.20711444228686479</v>
+        <v>0.214206274947531</v>
       </c>
       <c r="E36">
-        <v>0.1995785955927202</v>
+        <v>0.2056676051038841</v>
       </c>
       <c r="F36">
-        <v>0.19849469210412529</v>
+        <v>0.2079197061980149</v>
       </c>
       <c r="G36">
-        <v>0.2143360365599605</v>
+        <v>0.2224041913772364</v>
       </c>
       <c r="H36">
-        <v>0.30288260756198199</v>
+        <v>0.3057739225149511</v>
       </c>
       <c r="I36">
-        <v>0.41063102341912849</v>
+        <v>0.4229937368286139</v>
       </c>
       <c r="J36">
-        <v>0.39042266385784891</v>
+        <v>0.4060224531909635</v>
       </c>
       <c r="K36">
-        <v>0.36028093258619148</v>
+        <v>0.3700547970726564</v>
       </c>
       <c r="L36">
-        <v>0.32483158513574162</v>
+        <v>0.3235314912991337</v>
       </c>
       <c r="M36">
-        <v>0.33196864562362732</v>
+        <v>0.3213135693927744</v>
       </c>
       <c r="N36">
-        <v>0.38591712916732812</v>
+        <v>0.3818524276380806</v>
       </c>
       <c r="O36">
-        <v>0.45386035657739793</v>
+        <v>0.4491288036333294</v>
       </c>
       <c r="P36">
-        <v>0.50256669799943499</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>51</v>
+        <v>0.4997330511833563</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
+        </is>
       </c>
       <c r="B37">
-        <v>4.0053870276304582E-2</v>
+        <v>0.04349823847893455</v>
       </c>
       <c r="C37">
-        <v>0.17070849810258251</v>
+        <v>0.1679279626985467</v>
       </c>
       <c r="D37">
-        <v>0.2046908409103948</v>
+        <v>0.1997592940396759</v>
       </c>
       <c r="E37">
-        <v>0.201987888435844</v>
+        <v>0.1943789832013953</v>
       </c>
       <c r="F37">
-        <v>0.19964095883053071</v>
+        <v>0.1939896584912109</v>
       </c>
       <c r="G37">
-        <v>0.20990441635692719</v>
+        <v>0.2030036859104578</v>
       </c>
       <c r="H37">
-        <v>0.30510220514690972</v>
+        <v>0.2889199300188955</v>
       </c>
       <c r="I37">
-        <v>0.41757845168452012</v>
+        <v>0.4040001736430521</v>
       </c>
       <c r="J37">
-        <v>0.40292044598124688</v>
+        <v>0.3885214252503804</v>
       </c>
       <c r="K37">
-        <v>0.35923500535073177</v>
+        <v>0.3628045549126057</v>
       </c>
       <c r="L37">
-        <v>0.32579926283047023</v>
+        <v>0.3201523525116786</v>
       </c>
       <c r="M37">
-        <v>0.32108644680394982</v>
+        <v>0.3152154069722568</v>
       </c>
       <c r="N37">
-        <v>0.38219208692919743</v>
+        <v>0.3763720772631609</v>
       </c>
       <c r="O37">
-        <v>0.44109514350754758</v>
+        <v>0.4393036356329755</v>
       </c>
       <c r="P37">
-        <v>0.49482771734778452</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>52</v>
+        <v>0.4890038670516005</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
+        </is>
       </c>
       <c r="B38">
-        <v>4.8078134609302527E-2</v>
+        <v>0.04155257187642281</v>
       </c>
       <c r="C38">
-        <v>0.17858495907196081</v>
+        <v>0.1738352873460395</v>
       </c>
       <c r="D38">
-        <v>0.2147512744373726</v>
+        <v>0.2027772080366751</v>
       </c>
       <c r="E38">
-        <v>0.2018866250788921</v>
+        <v>0.19249090363431</v>
       </c>
       <c r="F38">
-        <v>0.20174938365873399</v>
+        <v>0.1934482051786397</v>
       </c>
       <c r="G38">
-        <v>0.21432296161388059</v>
+        <v>0.2027820336927711</v>
       </c>
       <c r="H38">
-        <v>0.29035749543317929</v>
+        <v>0.271570517022759</v>
       </c>
       <c r="I38">
-        <v>0.39604490203547282</v>
+        <v>0.3939673313103978</v>
       </c>
       <c r="J38">
-        <v>0.38117654565358122</v>
+        <v>0.3824915827064386</v>
       </c>
       <c r="K38">
-        <v>0.35658437287875561</v>
+        <v>0.3550134391850555</v>
       </c>
       <c r="L38">
-        <v>0.32129333629551321</v>
+        <v>0.3184820545706545</v>
       </c>
       <c r="M38">
-        <v>0.31289808562976779</v>
+        <v>0.3178890894678963</v>
       </c>
       <c r="N38">
-        <v>0.36730965432271939</v>
+        <v>0.3618187077667476</v>
       </c>
       <c r="O38">
-        <v>0.41804234184362338</v>
+        <v>0.4135379065633435</v>
       </c>
       <c r="P38">
-        <v>0.45801906455087449</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>53</v>
+        <v>0.4553120599069815</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B39">
-        <v>4.504332481385976E-2</v>
+        <v>0.04555977682679271</v>
       </c>
       <c r="C39">
-        <v>0.17731701716728759</v>
+        <v>0.1773911507470628</v>
       </c>
       <c r="D39">
-        <v>0.21411576692370521</v>
+        <v>0.2081991979765494</v>
       </c>
       <c r="E39">
-        <v>0.20466923690928959</v>
+        <v>0.2008381406787607</v>
       </c>
       <c r="F39">
-        <v>0.20611572931342531</v>
+        <v>0.1949828596321797</v>
       </c>
       <c r="G39">
-        <v>0.2156748001746939</v>
+        <v>0.2077304560472407</v>
       </c>
       <c r="H39">
-        <v>0.30118790429248549</v>
+        <v>0.2987582108309231</v>
       </c>
       <c r="I39">
-        <v>0.40488209986767798</v>
+        <v>0.3970494273833071</v>
       </c>
       <c r="J39">
-        <v>0.40067795313628829</v>
+        <v>0.3799856812141312</v>
       </c>
       <c r="K39">
-        <v>0.38163205849026188</v>
+        <v>0.3633884334054094</v>
       </c>
       <c r="L39">
-        <v>0.32795775717424708</v>
+        <v>0.3236460845061883</v>
       </c>
       <c r="M39">
-        <v>0.32195932461123478</v>
+        <v>0.3170482733570179</v>
       </c>
       <c r="N39">
-        <v>0.36375462703550437</v>
+        <v>0.3613415599965075</v>
       </c>
       <c r="O39">
-        <v>0.41947112967811417</v>
+        <v>0.4164314239919631</v>
       </c>
       <c r="P39">
-        <v>0.44699663775132781</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>54</v>
+        <v>0.4509523533264242</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+        </is>
       </c>
       <c r="B40">
-        <v>4.5771069874412783E-2</v>
+        <v>0.04639227603773026</v>
       </c>
       <c r="C40">
-        <v>0.17895797791160889</v>
+        <v>0.1718928971501663</v>
       </c>
       <c r="D40">
-        <v>0.21183556237459941</v>
+        <v>0.2017940867480949</v>
       </c>
       <c r="E40">
-        <v>0.2037676619859658</v>
+        <v>0.1929674213687571</v>
       </c>
       <c r="F40">
-        <v>0.19901619248849151</v>
+        <v>0.1918130265030843</v>
       </c>
       <c r="G40">
-        <v>0.20483602420641131</v>
+        <v>0.2039255024664994</v>
       </c>
       <c r="H40">
-        <v>0.27919750752919248</v>
+        <v>0.2764138293481136</v>
       </c>
       <c r="I40">
-        <v>0.37291467745340251</v>
+        <v>0.3814440864664244</v>
       </c>
       <c r="J40">
-        <v>0.37284644147069618</v>
+        <v>0.3737119048227646</v>
       </c>
       <c r="K40">
-        <v>0.33908770100941898</v>
+        <v>0.332578994745943</v>
       </c>
       <c r="L40">
-        <v>0.31203523236659492</v>
+        <v>0.3051825656125159</v>
       </c>
       <c r="M40">
-        <v>0.30736404116507943</v>
+        <v>0.294184632074025</v>
       </c>
       <c r="N40">
-        <v>0.32885904714359032</v>
+        <v>0.3173948291344849</v>
       </c>
       <c r="O40">
-        <v>0.37447525459146358</v>
+        <v>0.3682326724397665</v>
       </c>
       <c r="P40">
-        <v>0.38716163001658582</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>55</v>
+        <v>0.3742774468204298</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B41">
-        <v>5.3450153083555808E-2</v>
+        <v>0.05432047564549737</v>
       </c>
       <c r="C41">
-        <v>0.31181487006145231</v>
+        <v>0.3049164860778549</v>
       </c>
       <c r="D41">
-        <v>0.27609255601133531</v>
+        <v>0.2736498488468602</v>
       </c>
       <c r="E41">
-        <v>0.31106683116775602</v>
+        <v>0.3175838850125459</v>
       </c>
       <c r="F41">
-        <v>0.50501615676046685</v>
+        <v>0.5047921725479398</v>
       </c>
       <c r="G41">
-        <v>0.56576383543386577</v>
+        <v>0.5664847338429557</v>
       </c>
       <c r="H41">
-        <v>0.57776733738942843</v>
+        <v>0.5891374901243547</v>
       </c>
       <c r="I41">
-        <v>0.58066278105895253</v>
+        <v>0.5906777542797979</v>
       </c>
       <c r="J41">
-        <v>0.6350915236519481</v>
+        <v>0.636353443156788</v>
       </c>
       <c r="K41">
-        <v>0.67503138986100319</v>
+        <v>0.6648083153805608</v>
       </c>
       <c r="L41">
-        <v>0.71714608747182218</v>
+        <v>0.7120091150579537</v>
       </c>
       <c r="M41">
-        <v>0.79994976994809674</v>
+        <v>0.7921886657350313</v>
       </c>
       <c r="N41">
-        <v>0.78890682164107284</v>
+        <v>0.7803564699402451</v>
       </c>
       <c r="O41">
-        <v>0.78051288468306523</v>
+        <v>0.7710011043792375</v>
       </c>
       <c r="P41">
-        <v>0.78109322322384833</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>56</v>
+        <v>0.7701797214967647</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
+        </is>
       </c>
       <c r="B42">
-        <v>5.1987661865055497E-2</v>
+        <v>0.05137509443802854</v>
       </c>
       <c r="C42">
-        <v>0.24189453674942971</v>
+        <v>0.2360574096328902</v>
       </c>
       <c r="D42">
-        <v>0.23951136173393919</v>
+        <v>0.233396471215538</v>
       </c>
       <c r="E42">
-        <v>0.27657925919916582</v>
+        <v>0.2657566016303736</v>
       </c>
       <c r="F42">
-        <v>0.38737307673879529</v>
+        <v>0.3762446177672485</v>
       </c>
       <c r="G42">
-        <v>0.35531570361166398</v>
+        <v>0.3515616027960858</v>
       </c>
       <c r="H42">
-        <v>0.25840746864554992</v>
+        <v>0.2699666248656553</v>
       </c>
       <c r="I42">
-        <v>0.32094713773534422</v>
+        <v>0.3255388802144954</v>
       </c>
       <c r="J42">
-        <v>0.41780305596153361</v>
+        <v>0.4222400646698112</v>
       </c>
       <c r="K42">
-        <v>0.47042978596738422</v>
+        <v>0.4750892063533314</v>
       </c>
       <c r="L42">
-        <v>0.51215597282955727</v>
+        <v>0.5200532121993533</v>
       </c>
       <c r="M42">
-        <v>0.54088847410067376</v>
+        <v>0.54225071659226</v>
       </c>
       <c r="N42">
-        <v>0.53003676571001024</v>
+        <v>0.545437272836482</v>
       </c>
       <c r="O42">
-        <v>0.53918958923306204</v>
+        <v>0.5533990545995595</v>
       </c>
       <c r="P42">
-        <v>0.55724573317546455</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>57</v>
+        <v>0.5688157469196896</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+        </is>
       </c>
       <c r="B43">
-        <v>4.8874579088509847E-2</v>
+        <v>0.04722264403150864</v>
       </c>
       <c r="C43">
-        <v>0.22792485467224749</v>
+        <v>0.2243783614098249</v>
       </c>
       <c r="D43">
-        <v>0.21282520316638251</v>
+        <v>0.2059151097341408</v>
       </c>
       <c r="E43">
-        <v>0.2141003880477213</v>
+        <v>0.222416138351032</v>
       </c>
       <c r="F43">
-        <v>0.30773334055441048</v>
+        <v>0.3068234314415367</v>
       </c>
       <c r="G43">
-        <v>0.29500482174311898</v>
+        <v>0.2883934696935256</v>
       </c>
       <c r="H43">
-        <v>0.25477399269585088</v>
+        <v>0.2555970595343637</v>
       </c>
       <c r="I43">
-        <v>0.29003971008294882</v>
+        <v>0.2864417963807444</v>
       </c>
       <c r="J43">
-        <v>0.35292592682803958</v>
+        <v>0.3590444920623713</v>
       </c>
       <c r="K43">
-        <v>0.36926841991827908</v>
+        <v>0.3741343639197995</v>
       </c>
       <c r="L43">
-        <v>0.40705666017667652</v>
+        <v>0.4108804789865962</v>
       </c>
       <c r="M43">
-        <v>0.41046234612679522</v>
+        <v>0.4186320795935747</v>
       </c>
       <c r="N43">
-        <v>0.44611981268003148</v>
+        <v>0.4528903507404125</v>
       </c>
       <c r="O43">
-        <v>0.48102138140439038</v>
+        <v>0.4852552936141985</v>
       </c>
       <c r="P43">
-        <v>0.51290259990350751</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>58</v>
+        <v>0.5099243241761171</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
+        </is>
       </c>
       <c r="B44">
-        <v>8.2887880582324436E-2</v>
+        <v>0.08979066199600708</v>
       </c>
       <c r="C44">
-        <v>0.1467082700975893</v>
+        <v>0.1472738214290659</v>
       </c>
       <c r="D44">
-        <v>0.22768128910156041</v>
+        <v>0.2201153114811452</v>
       </c>
       <c r="E44">
-        <v>0.28870553640632979</v>
+        <v>0.2899603577921401</v>
       </c>
       <c r="F44">
-        <v>0.36586725740990178</v>
+        <v>0.3626934866553616</v>
       </c>
       <c r="G44">
-        <v>0.39009939911938663</v>
+        <v>0.3742145627519486</v>
       </c>
       <c r="H44">
-        <v>0.47722504940609478</v>
+        <v>0.4742428028216558</v>
       </c>
       <c r="I44">
-        <v>0.60376456555835667</v>
+        <v>0.6067027776668413</v>
       </c>
       <c r="J44">
-        <v>0.63516734514331641</v>
+        <v>0.6325871304113777</v>
       </c>
       <c r="K44">
-        <v>0.63091928324293645</v>
+        <v>0.6330649017941042</v>
       </c>
       <c r="L44">
-        <v>0.6431341659058385</v>
+        <v>0.643909906164314</v>
       </c>
       <c r="M44">
-        <v>0.64038256326931486</v>
+        <v>0.6387285118744379</v>
       </c>
       <c r="N44">
-        <v>0.67205335430993307</v>
+        <v>0.6683935828841713</v>
       </c>
       <c r="O44">
-        <v>0.72287633648192406</v>
+        <v>0.7189574028253837</v>
       </c>
       <c r="P44">
-        <v>0.80327811850322783</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>59</v>
+        <v>0.7928533657106144</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>adj_snv_sder_c(1,3,5)_</t>
+        </is>
       </c>
       <c r="B45">
-        <v>0.10301801259256629</v>
+        <v>0.1058896206023202</v>
       </c>
       <c r="C45">
-        <v>0.43786620237618312</v>
+        <v>0.4410850712289234</v>
       </c>
       <c r="D45">
-        <v>0.50161997657814272</v>
+        <v>0.5003971710068746</v>
       </c>
       <c r="E45">
-        <v>0.62683249625812998</v>
+        <v>0.6282526140637813</v>
       </c>
       <c r="F45">
-        <v>0.64064208826418856</v>
+        <v>0.6437224356871538</v>
       </c>
       <c r="G45">
-        <v>0.68246912633100887</v>
+        <v>0.6855215167918421</v>
       </c>
       <c r="H45">
-        <v>0.70612728306792127</v>
+        <v>0.7130817161397296</v>
       </c>
       <c r="I45">
-        <v>0.67502635898378427</v>
+        <v>0.6808356507027383</v>
       </c>
       <c r="J45">
-        <v>0.74906246646345132</v>
+        <v>0.7544115951662126</v>
       </c>
       <c r="K45">
-        <v>0.82540651069113313</v>
+        <v>0.8281414869826106</v>
       </c>
       <c r="L45">
-        <v>0.84816235836099463</v>
+        <v>0.8398971184299571</v>
       </c>
       <c r="M45">
-        <v>0.91075104103802684</v>
+        <v>0.9024050318672439</v>
       </c>
       <c r="N45">
-        <v>0.9925819222718204</v>
+        <v>0.981935856476256</v>
       </c>
       <c r="O45">
-        <v>1.0153239999466059</v>
+        <v>1.004031235956375</v>
       </c>
       <c r="P45">
-        <v>1.0320479882145359</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>60</v>
+        <v>1.024946856598736</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>adj_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B46">
-        <v>6.2602844495926777E-2</v>
+        <v>0.06377474949620875</v>
       </c>
       <c r="C46">
-        <v>0.19449214916753041</v>
+        <v>0.189594248909405</v>
       </c>
       <c r="D46">
-        <v>0.52528522399687549</v>
+        <v>0.5293744472987849</v>
       </c>
       <c r="E46">
-        <v>0.43587509232593302</v>
+        <v>0.4193143533626466</v>
       </c>
       <c r="F46">
-        <v>0.43455989452765281</v>
+        <v>0.4245558048059807</v>
       </c>
       <c r="G46">
-        <v>0.45082687829540008</v>
+        <v>0.4567855391576644</v>
       </c>
       <c r="H46">
-        <v>0.40373699891254161</v>
+        <v>0.3940960817792182</v>
       </c>
       <c r="I46">
-        <v>0.44190337283627429</v>
+        <v>0.4338331877671582</v>
       </c>
       <c r="J46">
-        <v>0.47388650893000972</v>
+        <v>0.4742329550980144</v>
       </c>
       <c r="K46">
-        <v>0.46073364772303932</v>
+        <v>0.4609181643633954</v>
       </c>
       <c r="L46">
-        <v>0.47681418622075922</v>
+        <v>0.4803032352449623</v>
       </c>
       <c r="M46">
-        <v>0.52245901707917441</v>
+        <v>0.5226968689199727</v>
       </c>
       <c r="N46">
-        <v>0.54989984726732055</v>
+        <v>0.5550735780129513</v>
       </c>
       <c r="O46">
-        <v>0.56468260003946225</v>
+        <v>0.5621846494759278</v>
       </c>
       <c r="P46">
-        <v>0.5980029279247735</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>61</v>
+        <v>0.6009431909895053</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
+        </is>
       </c>
       <c r="B47">
-        <v>5.634855445233139E-2</v>
+        <v>0.05579290190224231</v>
       </c>
       <c r="C47">
-        <v>0.22173318872772299</v>
+        <v>0.231114180643085</v>
       </c>
       <c r="D47">
-        <v>0.37003640205715083</v>
+        <v>0.3890874746400782</v>
       </c>
       <c r="E47">
-        <v>0.39058848670018231</v>
+        <v>0.4018955727375099</v>
       </c>
       <c r="F47">
-        <v>0.35590596173247918</v>
+        <v>0.3583000568902831</v>
       </c>
       <c r="G47">
-        <v>0.36708119277901469</v>
+        <v>0.3727986642218555</v>
       </c>
       <c r="H47">
-        <v>0.37594500429651329</v>
+        <v>0.3758687341271569</v>
       </c>
       <c r="I47">
-        <v>0.41713540599528842</v>
+        <v>0.4164878341761598</v>
       </c>
       <c r="J47">
-        <v>0.50107579172948091</v>
+        <v>0.5035788361327326</v>
       </c>
       <c r="K47">
-        <v>0.52255992954968633</v>
+        <v>0.5250790671107857</v>
       </c>
       <c r="L47">
-        <v>0.53947087660428816</v>
+        <v>0.5413269701550358</v>
       </c>
       <c r="M47">
-        <v>0.5735456042890672</v>
+        <v>0.5755306870862574</v>
       </c>
       <c r="N47">
-        <v>0.62033821364112285</v>
+        <v>0.6233694240826435</v>
       </c>
       <c r="O47">
-        <v>0.66859879998816607</v>
+        <v>0.6653932707161645</v>
       </c>
       <c r="P47">
-        <v>0.7035212997117315</v>
+        <v>0.7064732073585052</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:P19 B21:P47 B20:M20 O20:P20">
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="greaterThan">
-      <formula>0.2</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="lessThan">
-      <formula>0.2</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/ROSA_vitaSPEC/Results/test_pretraitements/ratio.alpha.beta/Resultats_ratio.alpha.beta_moy_diff.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/ratio.alpha.beta/Resultats_ratio.alpha.beta_moy_diff.xlsx
@@ -1,21 +1,205 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U108-N806\Documents\STAGE_M2_ROSA_NIRS\VitaSPEC\vitaspec_R\ROSA_vitaSPEC\Results\test_pretraitements\ratio.alpha.beta\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+  <si>
+    <t>Pretraitement</t>
+  </si>
+  <si>
+    <t>LV1_diff</t>
+  </si>
+  <si>
+    <t>LV2_diff</t>
+  </si>
+  <si>
+    <t>LV3_diff</t>
+  </si>
+  <si>
+    <t>LV4_diff</t>
+  </si>
+  <si>
+    <t>LV5_diff</t>
+  </si>
+  <si>
+    <t>LV6_diff</t>
+  </si>
+  <si>
+    <t>LV7_diff</t>
+  </si>
+  <si>
+    <t>LV8_diff</t>
+  </si>
+  <si>
+    <t>LV9_diff</t>
+  </si>
+  <si>
+    <t>LV10_diff</t>
+  </si>
+  <si>
+    <t>LV11_diff</t>
+  </si>
+  <si>
+    <t>LV12_diff</t>
+  </si>
+  <si>
+    <t>LV13_diff</t>
+  </si>
+  <si>
+    <t>LV14_diff</t>
+  </si>
+  <si>
+    <t>LV15_diff</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1000,1)_snv_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_msc_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_snv_sder_c(1,3,5)_</t>
+  </si>
+  <si>
+    <t>adj_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -61,13 +245,52 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -109,7 +332,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -141,9 +364,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -175,6 +399,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -350,2485 +575,2173 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P47"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:P43"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="51.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="16" width="12" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Pretraitement</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>LV1_diff</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>LV2_diff</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>LV3_diff</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>LV4_diff</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>LV5_diff</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>LV6_diff</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>LV7_diff</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>LV8_diff</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>LV9_diff</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>LV10_diff</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>LV11_diff</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>LV12_diff</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>LV13_diff</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>LV14_diff</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>LV15_diff</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1000,1)_snv_</t>
-        </is>
+    <row r="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>16</v>
       </c>
       <c r="B2">
-        <v>0.03904797754217491</v>
+        <v>4.2935817500231267E-2</v>
       </c>
       <c r="C2">
-        <v>0.08538607163223653</v>
+        <v>8.6658978485017482E-2</v>
       </c>
       <c r="D2">
-        <v>0.1207489735083802</v>
+        <v>0.1215590455052287</v>
       </c>
       <c r="E2">
-        <v>0.1583339649746449</v>
+        <v>0.1574000512940627</v>
       </c>
       <c r="F2">
-        <v>0.1838849101104164</v>
+        <v>0.18840061796888569</v>
       </c>
       <c r="G2">
-        <v>0.2755525823304284</v>
+        <v>0.27120802085424089</v>
       </c>
       <c r="H2">
-        <v>0.2502968322657916</v>
+        <v>0.24178671083298919</v>
       </c>
       <c r="I2">
-        <v>0.2614822225720915</v>
+        <v>0.25364392985650253</v>
       </c>
       <c r="J2">
-        <v>0.3485429813421914</v>
+        <v>0.3468226182723278</v>
       </c>
       <c r="K2">
-        <v>0.3619292792684995</v>
+        <v>0.34641463981832132</v>
       </c>
       <c r="L2">
-        <v>0.3882838349995015</v>
+        <v>0.38312786172457602</v>
       </c>
       <c r="M2">
-        <v>0.4034051666227304</v>
+        <v>0.39538633331671102</v>
       </c>
       <c r="N2">
-        <v>0.4066413927126138</v>
+        <v>0.40302984708987349</v>
       </c>
       <c r="O2">
-        <v>0.4037438123486587</v>
+        <v>0.39808822878929739</v>
       </c>
       <c r="P2">
-        <v>0.3746381475628773</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>0.37616953621852978</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>17</v>
       </c>
       <c r="B3">
-        <v>0.06237217781579563</v>
+        <v>6.4347812548356559E-2</v>
       </c>
       <c r="C3">
-        <v>0.1112077138765986</v>
+        <v>0.1108947752765245</v>
       </c>
       <c r="D3">
-        <v>0.5186837485391209</v>
+        <v>0.52396701449454219</v>
       </c>
       <c r="E3">
-        <v>0.3653780361348797</v>
+        <v>0.37436554530583538</v>
       </c>
       <c r="F3">
-        <v>0.3504825275394348</v>
+        <v>0.37092187572474011</v>
       </c>
       <c r="G3">
-        <v>0.334272156613693</v>
+        <v>0.33814931650705637</v>
       </c>
       <c r="H3">
-        <v>0.3821223699610294</v>
+        <v>0.3770482452130679</v>
       </c>
       <c r="I3">
-        <v>0.4253085086250326</v>
+        <v>0.42112281538802809</v>
       </c>
       <c r="J3">
-        <v>0.4037600626647871</v>
+        <v>0.40176121612258242</v>
       </c>
       <c r="K3">
-        <v>0.4021099365345735</v>
+        <v>0.39950526889231402</v>
       </c>
       <c r="L3">
-        <v>0.425630944755505</v>
+        <v>0.42554068247226851</v>
       </c>
       <c r="M3">
-        <v>0.4549698108840529</v>
+        <v>0.45380561904263289</v>
       </c>
       <c r="N3">
-        <v>0.5154417660020401</v>
+        <v>0.52080511001111585</v>
       </c>
       <c r="O3">
-        <v>0.5530980587630918</v>
+        <v>0.56412151846359215</v>
       </c>
       <c r="P3">
-        <v>0.5459661032523357</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_msc_</t>
-        </is>
+        <v>0.55236246888677998</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>18</v>
       </c>
       <c r="B4">
-        <v>0.04174701584896975</v>
+        <v>3.8366560742450227E-2</v>
       </c>
       <c r="C4">
-        <v>0.06419848535992394</v>
+        <v>6.6035040645732845E-2</v>
       </c>
       <c r="D4">
-        <v>0.1697862106554446</v>
+        <v>0.180069158756438</v>
       </c>
       <c r="E4">
-        <v>0.1775759463934417</v>
+        <v>0.1969110072613931</v>
       </c>
       <c r="F4">
-        <v>0.3432428877535393</v>
+        <v>0.37286992199741792</v>
       </c>
       <c r="G4">
-        <v>0.315797088899251</v>
+        <v>0.33615267790583608</v>
       </c>
       <c r="H4">
-        <v>0.3060232126559871</v>
+        <v>0.31568482581576618</v>
       </c>
       <c r="I4">
-        <v>0.3564725030807289</v>
+        <v>0.35982506108149043</v>
       </c>
       <c r="J4">
-        <v>0.3542801124487587</v>
+        <v>0.36499516543576138</v>
       </c>
       <c r="K4">
-        <v>0.3928904945154429</v>
+        <v>0.386580095136557</v>
       </c>
       <c r="L4">
-        <v>0.3938987717170199</v>
+        <v>0.39368529703722038</v>
       </c>
       <c r="M4">
-        <v>0.3909434739532833</v>
+        <v>0.39163376249085741</v>
       </c>
       <c r="N4">
-        <v>0.3850538295457803</v>
+        <v>0.39084327799462532</v>
       </c>
       <c r="O4">
-        <v>0.3967009351653133</v>
+        <v>0.39577926223375431</v>
       </c>
       <c r="P4">
-        <v>0.4159925063204992</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
-        </is>
+        <v>0.41811685041682972</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>19</v>
       </c>
       <c r="B5">
-        <v>0.04239356207431472</v>
+        <v>4.5396257096008218E-2</v>
       </c>
       <c r="C5">
-        <v>0.1358345324652967</v>
+        <v>0.13758928512125229</v>
       </c>
       <c r="D5">
-        <v>0.1738763280307555</v>
+        <v>0.18511440255207129</v>
       </c>
       <c r="E5">
-        <v>0.4612781786366424</v>
+        <v>0.46659495920847432</v>
       </c>
       <c r="F5">
-        <v>0.3250412069937172</v>
+        <v>0.32767803150853891</v>
       </c>
       <c r="G5">
-        <v>0.3681520295335126</v>
+        <v>0.38137268804680891</v>
       </c>
       <c r="H5">
-        <v>0.3635775175015543</v>
+        <v>0.37028209464916839</v>
       </c>
       <c r="I5">
-        <v>0.3580753830431493</v>
+        <v>0.3617132043135915</v>
       </c>
       <c r="J5">
-        <v>0.3272677293885392</v>
+        <v>0.3248829589090223</v>
       </c>
       <c r="K5">
-        <v>0.3250601114436255</v>
+        <v>0.31569187571913959</v>
       </c>
       <c r="L5">
-        <v>0.3271028748412628</v>
+        <v>0.31358623398989549</v>
       </c>
       <c r="M5">
-        <v>0.3478680583394126</v>
+        <v>0.33341892634020021</v>
       </c>
       <c r="N5">
-        <v>0.3920984834190143</v>
+        <v>0.37626966739936363</v>
       </c>
       <c r="O5">
-        <v>0.4266052800445939</v>
+        <v>0.4146740912249432</v>
       </c>
       <c r="P5">
-        <v>0.4702970154523893</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
-        </is>
+        <v>0.45942596922550699</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>20</v>
       </c>
       <c r="B6">
-        <v>0.04223873852203387</v>
+        <v>4.338747677706644E-2</v>
       </c>
       <c r="C6">
-        <v>0.1226263851590011</v>
+        <v>0.1247875410657992</v>
       </c>
       <c r="D6">
-        <v>0.1635617044837593</v>
+        <v>0.18341818319470171</v>
       </c>
       <c r="E6">
-        <v>0.4246733149127465</v>
+        <v>0.43764433856507651</v>
       </c>
       <c r="F6">
-        <v>0.2716921856500748</v>
+        <v>0.26506953686756629</v>
       </c>
       <c r="G6">
-        <v>0.2624129977840659</v>
+        <v>0.26764594237582318</v>
       </c>
       <c r="H6">
-        <v>0.2547887087074374</v>
+        <v>0.25536498001438929</v>
       </c>
       <c r="I6">
-        <v>0.2546005714779216</v>
+        <v>0.25158514513942681</v>
       </c>
       <c r="J6">
-        <v>0.2523257990960845</v>
+        <v>0.2459106920107435</v>
       </c>
       <c r="K6">
-        <v>0.2494667570491737</v>
+        <v>0.24733538742339509</v>
       </c>
       <c r="L6">
-        <v>0.2669911266077576</v>
+        <v>0.26311447418192019</v>
       </c>
       <c r="M6">
-        <v>0.286698585568124</v>
+        <v>0.28069925737692109</v>
       </c>
       <c r="N6">
-        <v>0.3153548150669507</v>
+        <v>0.31128707160766361</v>
       </c>
       <c r="O6">
-        <v>0.3249407560508691</v>
+        <v>0.32234934751311661</v>
       </c>
       <c r="P6">
-        <v>0.3578427321909708</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_</t>
-        </is>
+        <v>0.36019844576434662</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>21</v>
       </c>
       <c r="B7">
-        <v>0.04564740148382868</v>
+        <v>4.3462664949083601E-2</v>
       </c>
       <c r="C7">
-        <v>0.07353012749191674</v>
+        <v>7.1146610841139213E-2</v>
       </c>
       <c r="D7">
-        <v>0.1834122046838182</v>
+        <v>0.18010898101616279</v>
       </c>
       <c r="E7">
-        <v>0.228559399665533</v>
+        <v>0.22941863523212139</v>
       </c>
       <c r="F7">
-        <v>0.3017130055527922</v>
+        <v>0.30209588296635442</v>
       </c>
       <c r="G7">
-        <v>0.4002487211042144</v>
+        <v>0.41199818370380509</v>
       </c>
       <c r="H7">
-        <v>0.3349153214281435</v>
+        <v>0.34534653965002837</v>
       </c>
       <c r="I7">
-        <v>0.3177706444936819</v>
+        <v>0.32768482724584602</v>
       </c>
       <c r="J7">
-        <v>0.4082974707340994</v>
+        <v>0.4190372783605969</v>
       </c>
       <c r="K7">
-        <v>0.3839842562857768</v>
+        <v>0.38448714618319668</v>
       </c>
       <c r="L7">
-        <v>0.4093381015838943</v>
+        <v>0.40960423841230947</v>
       </c>
       <c r="M7">
-        <v>0.4336515608034748</v>
+        <v>0.43159973250387917</v>
       </c>
       <c r="N7">
-        <v>0.4075635202385682</v>
+        <v>0.40004016049611668</v>
       </c>
       <c r="O7">
-        <v>0.3989366996201565</v>
+        <v>0.38924785842588039</v>
       </c>
       <c r="P7">
-        <v>0.4007725263533218</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
-        </is>
+        <v>0.39141557781384312</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>22</v>
       </c>
       <c r="B8">
-        <v>0.03976775012989101</v>
+        <v>4.2219072336685849E-2</v>
       </c>
       <c r="C8">
-        <v>0.0619825775863721</v>
+        <v>6.521114976922103E-2</v>
       </c>
       <c r="D8">
-        <v>0.1650942481789164</v>
+        <v>0.16774469594701391</v>
       </c>
       <c r="E8">
-        <v>0.2968089706673592</v>
+        <v>0.29097308239357411</v>
       </c>
       <c r="F8">
-        <v>0.2977875912970573</v>
+        <v>0.30650124470600387</v>
       </c>
       <c r="G8">
-        <v>0.301275005951839</v>
+        <v>0.31085506044742178</v>
       </c>
       <c r="H8">
-        <v>0.3039868139218369</v>
+        <v>0.31696703978265489</v>
       </c>
       <c r="I8">
-        <v>0.3233770512071668</v>
+        <v>0.33598864571347492</v>
       </c>
       <c r="J8">
-        <v>0.3205148416890953</v>
+        <v>0.33742780231681291</v>
       </c>
       <c r="K8">
-        <v>0.3408905721491513</v>
+        <v>0.35268747411139389</v>
       </c>
       <c r="L8">
-        <v>0.3624086588759518</v>
+        <v>0.38577619585584783</v>
       </c>
       <c r="M8">
-        <v>0.3594368107842359</v>
+        <v>0.37800157772235032</v>
       </c>
       <c r="N8">
-        <v>0.3443747611822146</v>
+        <v>0.36205561398444192</v>
       </c>
       <c r="O8">
-        <v>0.3560357704553392</v>
+        <v>0.3783294161896571</v>
       </c>
       <c r="P8">
-        <v>0.3800728809808698</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
-        </is>
+        <v>0.39751330116919559</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>23</v>
       </c>
       <c r="B9">
-        <v>0.03652986883185227</v>
+        <v>3.9879828910231667E-2</v>
       </c>
       <c r="C9">
-        <v>0.05823031216397123</v>
+        <v>6.3942188116186724E-2</v>
       </c>
       <c r="D9">
-        <v>0.1564304163297987</v>
+        <v>0.15621849170379279</v>
       </c>
       <c r="E9">
-        <v>0.2590297529684507</v>
+        <v>0.26803683592703631</v>
       </c>
       <c r="F9">
-        <v>0.2697899475540978</v>
+        <v>0.27195862856851238</v>
       </c>
       <c r="G9">
-        <v>0.2581722006512554</v>
+        <v>0.26615228832735682</v>
       </c>
       <c r="H9">
-        <v>0.2529193721271513</v>
+        <v>0.26760720115898889</v>
       </c>
       <c r="I9">
-        <v>0.2604649687591896</v>
+        <v>0.27691240090898789</v>
       </c>
       <c r="J9">
-        <v>0.2524982330256135</v>
+        <v>0.26565899799032672</v>
       </c>
       <c r="K9">
-        <v>0.2447550939506252</v>
+        <v>0.2451697147164279</v>
       </c>
       <c r="L9">
-        <v>0.2714853074601899</v>
+        <v>0.27957557854231269</v>
       </c>
       <c r="M9">
-        <v>0.2535562725043113</v>
+        <v>0.26095368650093081</v>
       </c>
       <c r="N9">
-        <v>0.2443356353628868</v>
+        <v>0.249284736915002</v>
       </c>
       <c r="O9">
-        <v>0.2535254974553028</v>
+        <v>0.25402355116296071</v>
       </c>
       <c r="P9">
-        <v>0.2763702470106977</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
-        </is>
+        <v>0.27949945674115312</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>24</v>
       </c>
       <c r="B10">
-        <v>0.0401850507633475</v>
+        <v>3.8213199905875003E-2</v>
       </c>
       <c r="C10">
-        <v>0.06451801311481949</v>
+        <v>6.1769049813525642E-2</v>
       </c>
       <c r="D10">
-        <v>0.1599553813970611</v>
+        <v>0.165089390266728</v>
       </c>
       <c r="E10">
-        <v>0.2607118672994512</v>
+        <v>0.26934777009283539</v>
       </c>
       <c r="F10">
-        <v>0.2659229201589506</v>
+        <v>0.27940932668750079</v>
       </c>
       <c r="G10">
-        <v>0.2702357431826899</v>
+        <v>0.27253504101947001</v>
       </c>
       <c r="H10">
-        <v>0.2653719203769795</v>
+        <v>0.26642526856610382</v>
       </c>
       <c r="I10">
-        <v>0.2656232945816254</v>
+        <v>0.27416862411646797</v>
       </c>
       <c r="J10">
-        <v>0.2565160756598046</v>
+        <v>0.26867604681826163</v>
       </c>
       <c r="K10">
-        <v>0.2450925791713608</v>
+        <v>0.25093642668347871</v>
       </c>
       <c r="L10">
-        <v>0.2839215760617818</v>
+        <v>0.28737976630909268</v>
       </c>
       <c r="M10">
-        <v>0.2627963999045714</v>
+        <v>0.2702297361595285</v>
       </c>
       <c r="N10">
-        <v>0.2474535627719827</v>
+        <v>0.26145805496011298</v>
       </c>
       <c r="O10">
-        <v>0.2571140093968639</v>
+        <v>0.26222657603919891</v>
       </c>
       <c r="P10">
-        <v>0.2784705399254995</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-        </is>
+        <v>0.2855063935577869</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>25</v>
       </c>
       <c r="B11">
-        <v>0.03922593793121484</v>
+        <v>4.3251474635265658E-2</v>
       </c>
       <c r="C11">
-        <v>0.06396984370076635</v>
+        <v>6.8186631803990705E-2</v>
       </c>
       <c r="D11">
-        <v>0.1670854651232089</v>
+        <v>0.1638021419563063</v>
       </c>
       <c r="E11">
-        <v>0.2787370775670883</v>
+        <v>0.27223438247187232</v>
       </c>
       <c r="F11">
-        <v>0.2857753424197272</v>
+        <v>0.27573399722945863</v>
       </c>
       <c r="G11">
-        <v>0.2612047820972633</v>
+        <v>0.27304150763915758</v>
       </c>
       <c r="H11">
-        <v>0.2729815816714161</v>
+        <v>0.27599215355044898</v>
       </c>
       <c r="I11">
-        <v>0.2701818392410086</v>
+        <v>0.27286984749441662</v>
       </c>
       <c r="J11">
-        <v>0.2623128037076604</v>
+        <v>0.26721214113558828</v>
       </c>
       <c r="K11">
-        <v>0.2422911404280707</v>
+        <v>0.24085342429286391</v>
       </c>
       <c r="L11">
-        <v>0.2708732997191711</v>
+        <v>0.2718006986614761</v>
       </c>
       <c r="M11">
-        <v>0.252432030411266</v>
+        <v>0.25834127731036882</v>
       </c>
       <c r="N11">
-        <v>0.2436653093594777</v>
+        <v>0.2486256621128792</v>
       </c>
       <c r="O11">
-        <v>0.2561810415983424</v>
+        <v>0.2583820670654573</v>
       </c>
       <c r="P11">
-        <v>0.2710669877150534</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
-        </is>
+        <v>0.27419993612868238</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>26</v>
       </c>
       <c r="B12">
-        <v>0.04256528276193421</v>
+        <v>4.7306232736826173E-2</v>
       </c>
       <c r="C12">
-        <v>0.1362916881376861</v>
+        <v>0.1446094076247906</v>
       </c>
       <c r="D12">
-        <v>0.1728722892940577</v>
+        <v>0.1578145800666067</v>
       </c>
       <c r="E12">
-        <v>0.4094854087606609</v>
+        <v>0.39115226970301098</v>
       </c>
       <c r="F12">
-        <v>0.3535258999053699</v>
+        <v>0.33489522237022112</v>
       </c>
       <c r="G12">
-        <v>0.3607680679800526</v>
+        <v>0.34384844170281009</v>
       </c>
       <c r="H12">
-        <v>0.337676498526142</v>
+        <v>0.3381614291749333</v>
       </c>
       <c r="I12">
-        <v>0.304778781504616</v>
+        <v>0.31170793517803908</v>
       </c>
       <c r="J12">
-        <v>0.292115596851576</v>
+        <v>0.30027889325653118</v>
       </c>
       <c r="K12">
-        <v>0.2879512478717307</v>
+        <v>0.29877041186417241</v>
       </c>
       <c r="L12">
-        <v>0.2933678139035074</v>
+        <v>0.30186103509520629</v>
       </c>
       <c r="M12">
-        <v>0.3130706302910846</v>
+        <v>0.3189920146731221</v>
       </c>
       <c r="N12">
-        <v>0.3486005259592077</v>
+        <v>0.35460353615871892</v>
       </c>
       <c r="O12">
-        <v>0.3853151573120642</v>
+        <v>0.39287124807613433</v>
       </c>
       <c r="P12">
-        <v>0.4466001436410882</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
-        </is>
+        <v>0.45529172945674462</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>27</v>
       </c>
       <c r="B13">
-        <v>0.05322642830315513</v>
+        <v>4.8405333262818047E-2</v>
       </c>
       <c r="C13">
-        <v>0.2121951081227109</v>
+        <v>0.21328986309586631</v>
       </c>
       <c r="D13">
-        <v>0.2759767924593327</v>
+        <v>0.27213570209588039</v>
       </c>
       <c r="E13">
-        <v>0.3867167806037138</v>
+        <v>0.38277105126073779</v>
       </c>
       <c r="F13">
-        <v>0.5041365460845322</v>
+        <v>0.50028978954772274</v>
       </c>
       <c r="G13">
-        <v>0.4763717648760747</v>
+        <v>0.48517808759609221</v>
       </c>
       <c r="H13">
-        <v>0.5511790204978742</v>
+        <v>0.5579563146911023</v>
       </c>
       <c r="I13">
-        <v>0.5347655314171949</v>
+        <v>0.54128947002417804</v>
       </c>
       <c r="J13">
-        <v>0.5159268377250056</v>
+        <v>0.52005095539285928</v>
       </c>
       <c r="K13">
-        <v>0.481766407826129</v>
+        <v>0.49334016892839688</v>
       </c>
       <c r="L13">
-        <v>0.4955998637366919</v>
+        <v>0.495027742792992</v>
       </c>
       <c r="M13">
-        <v>0.5097570385038137</v>
+        <v>0.50326119435604688</v>
       </c>
       <c r="N13">
-        <v>0.5118630701557418</v>
+        <v>0.50492862241710346</v>
       </c>
       <c r="O13">
-        <v>0.5220565613991389</v>
+        <v>0.51448726508283038</v>
       </c>
       <c r="P13">
-        <v>0.5584586806784242</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-        </is>
+        <v>0.55218796228479605</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>28</v>
       </c>
       <c r="B14">
-        <v>0.04115659675395007</v>
+        <v>4.0199252903591581E-2</v>
       </c>
       <c r="C14">
-        <v>0.06975238279574272</v>
+        <v>7.0305039833459995E-2</v>
       </c>
       <c r="D14">
-        <v>0.1728598097078283</v>
+        <v>0.17433561433128261</v>
       </c>
       <c r="E14">
-        <v>0.2138411979817406</v>
+        <v>0.2104311522972783</v>
       </c>
       <c r="F14">
-        <v>0.2893750914344916</v>
+        <v>0.27829598152644619</v>
       </c>
       <c r="G14">
-        <v>0.3715746193618945</v>
+        <v>0.3664923868985327</v>
       </c>
       <c r="H14">
-        <v>0.3059386672332959</v>
+        <v>0.30268273106037857</v>
       </c>
       <c r="I14">
-        <v>0.2795530751696481</v>
+        <v>0.27125204211131748</v>
       </c>
       <c r="J14">
-        <v>0.3665783349860826</v>
+        <v>0.35717196512811572</v>
       </c>
       <c r="K14">
-        <v>0.4221182355741246</v>
+        <v>0.41905139221489601</v>
       </c>
       <c r="L14">
-        <v>0.3295785394338905</v>
+        <v>0.32692378499390728</v>
       </c>
       <c r="M14">
-        <v>0.3224031133523147</v>
+        <v>0.32146446121730748</v>
       </c>
       <c r="N14">
-        <v>0.2997555493586959</v>
+        <v>0.2975097757365307</v>
       </c>
       <c r="O14">
-        <v>0.2996907885588004</v>
+        <v>0.29926229786607278</v>
       </c>
       <c r="P14">
-        <v>0.2900974313510516</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-        </is>
+        <v>0.29676107044405808</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>29</v>
       </c>
       <c r="B15">
-        <v>0.04501907555915822</v>
+        <v>4.0395869918111733E-2</v>
       </c>
       <c r="C15">
-        <v>0.07479856121295549</v>
+        <v>6.7003569192856965E-2</v>
       </c>
       <c r="D15">
-        <v>0.178170451428755</v>
+        <v>0.1688487447439041</v>
       </c>
       <c r="E15">
-        <v>0.2150232514046166</v>
+        <v>0.20531986881050721</v>
       </c>
       <c r="F15">
-        <v>0.2902880387907631</v>
+        <v>0.26693159327821481</v>
       </c>
       <c r="G15">
-        <v>0.3792363593779841</v>
+        <v>0.35097627962248551</v>
       </c>
       <c r="H15">
-        <v>0.3068490133076775</v>
+        <v>0.29300495016355588</v>
       </c>
       <c r="I15">
-        <v>0.2784406385786257</v>
+        <v>0.27090128048877388</v>
       </c>
       <c r="J15">
-        <v>0.3790638674538088</v>
+        <v>0.35519635073235828</v>
       </c>
       <c r="K15">
-        <v>0.4108053112201011</v>
+        <v>0.3995425898839533</v>
       </c>
       <c r="L15">
-        <v>0.3247926175500198</v>
+        <v>0.32573821882603871</v>
       </c>
       <c r="M15">
-        <v>0.3191626380447133</v>
+        <v>0.32501432120347579</v>
       </c>
       <c r="N15">
-        <v>0.2939425320865534</v>
+        <v>0.29656035808874631</v>
       </c>
       <c r="O15">
-        <v>0.2944973910606898</v>
+        <v>0.29199458253889432</v>
       </c>
       <c r="P15">
-        <v>0.2851771948836732</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
-        </is>
+        <v>0.29196382736048132</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>30</v>
       </c>
       <c r="B16">
-        <v>0.04198764201915543</v>
+        <v>4.0262952902623932E-2</v>
       </c>
       <c r="C16">
-        <v>0.06780673298023737</v>
+        <v>6.919816339428056E-2</v>
       </c>
       <c r="D16">
-        <v>0.1682606073615877</v>
+        <v>0.17052865070341541</v>
       </c>
       <c r="E16">
-        <v>0.2067519521889673</v>
+        <v>0.2042857926190115</v>
       </c>
       <c r="F16">
-        <v>0.2681016603345417</v>
+        <v>0.27371860442426182</v>
       </c>
       <c r="G16">
-        <v>0.3601618990950864</v>
+        <v>0.35514365431265432</v>
       </c>
       <c r="H16">
-        <v>0.301473010875261</v>
+        <v>0.29929482008797093</v>
       </c>
       <c r="I16">
-        <v>0.2658593135085411</v>
+        <v>0.26298416096540911</v>
       </c>
       <c r="J16">
-        <v>0.3529371003323257</v>
+        <v>0.34510140220207008</v>
       </c>
       <c r="K16">
-        <v>0.3249077142243038</v>
+        <v>0.32411399175691419</v>
       </c>
       <c r="L16">
-        <v>0.316893472145883</v>
+        <v>0.31232497212513832</v>
       </c>
       <c r="M16">
-        <v>0.3062893264936263</v>
+        <v>0.30797664875400399</v>
       </c>
       <c r="N16">
-        <v>0.2763186454304307</v>
+        <v>0.27576405665050108</v>
       </c>
       <c r="O16">
-        <v>0.2740923900155002</v>
+        <v>0.2770600697718768</v>
       </c>
       <c r="P16">
-        <v>0.2740510259329297</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-        </is>
+        <v>0.27307501729741268</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>31</v>
       </c>
       <c r="B17">
-        <v>0.03869027236601501</v>
+        <v>4.4712139802813751E-2</v>
       </c>
       <c r="C17">
-        <v>0.07011588415315817</v>
+        <v>7.488727236368671E-2</v>
       </c>
       <c r="D17">
-        <v>0.1745367320525192</v>
+        <v>0.17890083033484969</v>
       </c>
       <c r="E17">
-        <v>0.2085823933320769</v>
+        <v>0.21838474875417119</v>
       </c>
       <c r="F17">
-        <v>0.2673207987310122</v>
+        <v>0.27974765913077959</v>
       </c>
       <c r="G17">
-        <v>0.3577051848628112</v>
+        <v>0.36046846262340221</v>
       </c>
       <c r="H17">
-        <v>0.2946777382968144</v>
+        <v>0.30351364694026062</v>
       </c>
       <c r="I17">
-        <v>0.2638843046805847</v>
+        <v>0.27215474602367912</v>
       </c>
       <c r="J17">
-        <v>0.3560615054985022</v>
+        <v>0.36075612733708867</v>
       </c>
       <c r="K17">
-        <v>0.3561193145028001</v>
+        <v>0.3656844633611257</v>
       </c>
       <c r="L17">
-        <v>0.3313400684975948</v>
+        <v>0.33841144205533019</v>
       </c>
       <c r="M17">
-        <v>0.3177289722488921</v>
+        <v>0.32332506047919118</v>
       </c>
       <c r="N17">
-        <v>0.3003966191676157</v>
+        <v>0.30051135179311728</v>
       </c>
       <c r="O17">
-        <v>0.2968666115770855</v>
+        <v>0.2951889752135865</v>
       </c>
       <c r="P17">
-        <v>0.2915674129934955</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-        </is>
+        <v>0.28844938001836279</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>32</v>
       </c>
       <c r="B18">
-        <v>0.04316359209887288</v>
+        <v>4.4252251334848877E-2</v>
       </c>
       <c r="C18">
-        <v>0.1378703546360111</v>
+        <v>0.14060862084059589</v>
       </c>
       <c r="D18">
-        <v>0.1774012863044894</v>
+        <v>0.18395072258080911</v>
       </c>
       <c r="E18">
-        <v>0.4349065045604881</v>
+        <v>0.43129458403197868</v>
       </c>
       <c r="F18">
-        <v>0.3189266056179478</v>
+        <v>0.33304020677311269</v>
       </c>
       <c r="G18">
-        <v>0.3554979010068385</v>
+        <v>0.35967996247995743</v>
       </c>
       <c r="H18">
-        <v>0.334522071661597</v>
+        <v>0.33765350172001729</v>
       </c>
       <c r="I18">
-        <v>0.3324707833883523</v>
+        <v>0.34365512378904989</v>
       </c>
       <c r="J18">
-        <v>0.3053734886072024</v>
+        <v>0.30770628504352898</v>
       </c>
       <c r="K18">
-        <v>0.3010038247275956</v>
+        <v>0.30355242499737511</v>
       </c>
       <c r="L18">
-        <v>0.3079658660310806</v>
+        <v>0.30512617868898262</v>
       </c>
       <c r="M18">
-        <v>0.3217296587195967</v>
+        <v>0.32408814103493011</v>
       </c>
       <c r="N18">
-        <v>0.3694686693905328</v>
+        <v>0.36849052998404602</v>
       </c>
       <c r="O18">
-        <v>0.4103541622679898</v>
+        <v>0.41557641389551359</v>
       </c>
       <c r="P18">
-        <v>0.4510578555953885</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
-        </is>
+        <v>0.45311002710530768</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>33</v>
       </c>
       <c r="B19">
-        <v>0.04302431015676204</v>
+        <v>4.2259474757734922E-2</v>
       </c>
       <c r="C19">
-        <v>0.1295696830297616</v>
+        <v>0.1258355061414318</v>
       </c>
       <c r="D19">
-        <v>0.1844766799669996</v>
+        <v>0.19018866329809181</v>
       </c>
       <c r="E19">
-        <v>0.4352880343932952</v>
+        <v>0.44070614944869729</v>
       </c>
       <c r="F19">
-        <v>0.2902268086242805</v>
+        <v>0.30131343112013081</v>
       </c>
       <c r="G19">
-        <v>0.2801534605543784</v>
+        <v>0.28151113346340328</v>
       </c>
       <c r="H19">
-        <v>0.2717039642664086</v>
+        <v>0.28020867480730399</v>
       </c>
       <c r="I19">
-        <v>0.2538813161926359</v>
+        <v>0.25802597544524097</v>
       </c>
       <c r="J19">
-        <v>0.2475759429187336</v>
+        <v>0.25022120631142519</v>
       </c>
       <c r="K19">
-        <v>0.2545718579962797</v>
+        <v>0.26139113915052647</v>
       </c>
       <c r="L19">
-        <v>0.276233775663222</v>
+        <v>0.28072296365136268</v>
       </c>
       <c r="M19">
-        <v>0.2960438733593971</v>
+        <v>0.3026073254996145</v>
       </c>
       <c r="N19">
-        <v>0.3317607414392896</v>
+        <v>0.33954782243611947</v>
       </c>
       <c r="O19">
-        <v>0.3381467845672324</v>
+        <v>0.34296362106222772</v>
       </c>
       <c r="P19">
-        <v>0.3644970762190642</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-        </is>
+        <v>0.36916902526437978</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>34</v>
       </c>
       <c r="B20">
-        <v>0.04109496151105804</v>
+        <v>4.2635650868529287E-2</v>
       </c>
       <c r="C20">
-        <v>0.0958436872106963</v>
+        <v>0.1101558086357243</v>
       </c>
       <c r="D20">
-        <v>0.2124932073090348</v>
+        <v>0.2083619920480908</v>
       </c>
       <c r="E20">
-        <v>0.2856690854116579</v>
+        <v>0.28320621758677189</v>
       </c>
       <c r="F20">
-        <v>0.2398939657363673</v>
+        <v>0.24242129090126779</v>
       </c>
       <c r="G20">
-        <v>0.3278749209918272</v>
+        <v>0.32449580972354541</v>
       </c>
       <c r="H20">
-        <v>0.2677259656275432</v>
+        <v>0.2566784138026848</v>
       </c>
       <c r="I20">
-        <v>0.2510245224334115</v>
+        <v>0.24347451492941141</v>
       </c>
       <c r="J20">
-        <v>0.2360431247944298</v>
+        <v>0.2345647092736084</v>
       </c>
       <c r="K20">
-        <v>0.2388654050970878</v>
+        <v>0.22867160041927101</v>
       </c>
       <c r="L20">
-        <v>0.2571392815914986</v>
+        <v>0.24849515369054481</v>
       </c>
       <c r="M20">
-        <v>0.2959763709693907</v>
+        <v>0.29051005053661111</v>
       </c>
       <c r="N20">
-        <v>0.2669356537015624</v>
+        <v>0.2617843977283062</v>
       </c>
       <c r="O20">
-        <v>0.2898067722042237</v>
+        <v>0.28784091081488489</v>
       </c>
       <c r="P20">
-        <v>0.3144747339607464</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>0.30882146081871897</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>35</v>
       </c>
       <c r="B21">
-        <v>0.06165924729854524</v>
+        <v>6.2263980303566092E-2</v>
       </c>
       <c r="C21">
-        <v>0.1020424741433353</v>
+        <v>0.10208700522354019</v>
       </c>
       <c r="D21">
-        <v>0.4730261008971418</v>
+        <v>0.45716587388873281</v>
       </c>
       <c r="E21">
-        <v>0.3448547362150225</v>
+        <v>0.32765588121588862</v>
       </c>
       <c r="F21">
-        <v>0.3449109648777063</v>
+        <v>0.32324135602712212</v>
       </c>
       <c r="G21">
-        <v>0.3551632036505384</v>
+        <v>0.34025627437674871</v>
       </c>
       <c r="H21">
-        <v>0.4119218018128617</v>
+        <v>0.40650910812506891</v>
       </c>
       <c r="I21">
-        <v>0.4536300191980963</v>
+        <v>0.43883582832420021</v>
       </c>
       <c r="J21">
-        <v>0.4087232213225347</v>
+        <v>0.40677707810006941</v>
       </c>
       <c r="K21">
-        <v>0.4151733944082412</v>
+        <v>0.41495505082097389</v>
       </c>
       <c r="L21">
-        <v>0.4222606353918158</v>
+        <v>0.42140172881681931</v>
       </c>
       <c r="M21">
-        <v>0.4585925746740792</v>
+        <v>0.45989197938031562</v>
       </c>
       <c r="N21">
-        <v>0.5130791625835267</v>
+        <v>0.51758939721679642</v>
       </c>
       <c r="O21">
-        <v>0.558283842434431</v>
+        <v>0.55884157898021791</v>
       </c>
       <c r="P21">
-        <v>0.5660207990045247</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>0.57326078457772867</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>36</v>
       </c>
       <c r="B22">
-        <v>0.06267963026293685</v>
+        <v>6.2880643666395356E-2</v>
       </c>
       <c r="C22">
-        <v>0.1039261732416468</v>
+        <v>0.1051161708099935</v>
       </c>
       <c r="D22">
-        <v>0.465274365787498</v>
+        <v>0.45921084045842181</v>
       </c>
       <c r="E22">
-        <v>0.3245379026990681</v>
+        <v>0.32211081190591567</v>
       </c>
       <c r="F22">
-        <v>0.3289095910332301</v>
+        <v>0.3265228723605868</v>
       </c>
       <c r="G22">
-        <v>0.3466101063454723</v>
+        <v>0.34246993088394961</v>
       </c>
       <c r="H22">
-        <v>0.4215363934574069</v>
+        <v>0.41497743886005473</v>
       </c>
       <c r="I22">
-        <v>0.4705739409802746</v>
+        <v>0.461602221560101</v>
       </c>
       <c r="J22">
-        <v>0.4331666223979143</v>
+        <v>0.42985116978161703</v>
       </c>
       <c r="K22">
-        <v>0.4454418786746462</v>
+        <v>0.43788160509695051</v>
       </c>
       <c r="L22">
-        <v>0.4736269182528977</v>
+        <v>0.46016475682651559</v>
       </c>
       <c r="M22">
-        <v>0.5015813825524974</v>
+        <v>0.49341082296276723</v>
       </c>
       <c r="N22">
-        <v>0.5427699932191442</v>
+        <v>0.53549778628843303</v>
       </c>
       <c r="O22">
-        <v>0.5653417999413026</v>
+        <v>0.55439188153114638</v>
       </c>
       <c r="P22">
-        <v>0.5860202396173591</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>0.57666240705089833</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>37</v>
       </c>
       <c r="B23">
-        <v>0.04505083777502146</v>
+        <v>4.6750661845032758E-2</v>
       </c>
       <c r="C23">
-        <v>0.2128460637855387</v>
+        <v>0.21514265318494599</v>
       </c>
       <c r="D23">
-        <v>0.1761055979689771</v>
+        <v>0.1820365226877749</v>
       </c>
       <c r="E23">
-        <v>0.204437335232499</v>
+        <v>0.2147221154363316</v>
       </c>
       <c r="F23">
-        <v>0.2510729099709016</v>
+        <v>0.25784158556628839</v>
       </c>
       <c r="G23">
-        <v>0.2492951426416379</v>
+        <v>0.25751733109757441</v>
       </c>
       <c r="H23">
-        <v>0.2650598926047852</v>
+        <v>0.27399327841718257</v>
       </c>
       <c r="I23">
-        <v>0.2935949943918194</v>
+        <v>0.30159461435641982</v>
       </c>
       <c r="J23">
-        <v>0.2982629961163693</v>
+        <v>0.30523707923087989</v>
       </c>
       <c r="K23">
-        <v>0.342504728757715</v>
+        <v>0.3407979421816128</v>
       </c>
       <c r="L23">
-        <v>0.3757420421604451</v>
+        <v>0.37039440829056902</v>
       </c>
       <c r="M23">
-        <v>0.4357646926090479</v>
+        <v>0.4272996077773703</v>
       </c>
       <c r="N23">
-        <v>0.4600218898258338</v>
+        <v>0.45874423165825651</v>
       </c>
       <c r="O23">
-        <v>0.4919302331200235</v>
+        <v>0.49233195499329607</v>
       </c>
       <c r="P23">
-        <v>0.5359141175397575</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>adj_red_c(950,20,1)_snv_sder_c(1,3,15)_</t>
-        </is>
+        <v>0.53484536665880533</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>38</v>
       </c>
       <c r="B24">
-        <v>0.1579540895918941</v>
+        <v>4.3469224710414082E-2</v>
       </c>
       <c r="C24">
-        <v>0.1353666226516572</v>
+        <v>0.1613631653616466</v>
       </c>
       <c r="D24">
-        <v>0.1765178073307431</v>
+        <v>0.19507734971223381</v>
       </c>
       <c r="E24">
-        <v>0.2577407261703716</v>
+        <v>0.1951054153728434</v>
       </c>
       <c r="F24">
-        <v>0.385726349256477</v>
+        <v>0.23628574530107499</v>
       </c>
       <c r="G24">
-        <v>0.6105225624586138</v>
+        <v>0.22668994642021081</v>
       </c>
       <c r="H24">
-        <v>0.6241916651076647</v>
+        <v>0.34199089229102209</v>
       </c>
       <c r="I24">
-        <v>0.6934543070802517</v>
+        <v>0.42542339710802429</v>
       </c>
       <c r="J24">
-        <v>0.8120487402058589</v>
+        <v>0.439570508884083</v>
       </c>
       <c r="K24">
-        <v>1.008958228882128</v>
+        <v>0.43219349251134781</v>
       </c>
       <c r="L24">
-        <v>1.049274923210439</v>
+        <v>0.44604709099348638</v>
       </c>
       <c r="M24">
-        <v>1.121577201357097</v>
+        <v>0.53319066097715662</v>
       </c>
       <c r="N24">
-        <v>1.231050830125415</v>
+        <v>0.65458274324828147</v>
       </c>
       <c r="O24">
-        <v>1.330567408951456</v>
+        <v>0.73039196245280669</v>
       </c>
       <c r="P24">
-        <v>1.439471443309416</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>adj_red_c(950,20,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>0.8159419196143658</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>39</v>
       </c>
       <c r="B25">
-        <v>0.4549330591330902</v>
+        <v>4.4086719637755012E-2</v>
       </c>
       <c r="C25">
-        <v>0.4324093107559615</v>
+        <v>0.17906795339540979</v>
       </c>
       <c r="D25">
-        <v>0.4631005065975493</v>
+        <v>0.20921606045893359</v>
       </c>
       <c r="E25">
-        <v>0.503216455558521</v>
+        <v>0.20581834623209361</v>
       </c>
       <c r="F25">
-        <v>0.6618735724794155</v>
+        <v>0.2109393413792027</v>
       </c>
       <c r="G25">
-        <v>0.7557095614557708</v>
+        <v>0.24370520631045681</v>
       </c>
       <c r="H25">
-        <v>0.8179060250498315</v>
+        <v>0.36180212686654151</v>
       </c>
       <c r="I25">
-        <v>0.8493556138074505</v>
+        <v>0.53175565729759766</v>
       </c>
       <c r="J25">
-        <v>0.8960251143300175</v>
+        <v>0.51756058722435216</v>
       </c>
       <c r="K25">
-        <v>1.033459164549201</v>
+        <v>0.47293197824689259</v>
       </c>
       <c r="L25">
-        <v>1.108378539221623</v>
+        <v>0.46829349371037299</v>
       </c>
       <c r="M25">
-        <v>1.260002993206105</v>
+        <v>0.49643235727921858</v>
       </c>
       <c r="N25">
-        <v>1.387834343541871</v>
+        <v>0.57882910381413466</v>
       </c>
       <c r="O25">
-        <v>1.462302307108179</v>
+        <v>0.67961440977603205</v>
       </c>
       <c r="P25">
-        <v>1.500067107220984</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>adj_red_c(950,750,1)_snv_sder_c(1,3,15)_</t>
-        </is>
+        <v>0.76224541330336137</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>40</v>
       </c>
       <c r="B26">
-        <v>0.1449490457115274</v>
+        <v>3.960928808895485E-2</v>
       </c>
       <c r="C26">
-        <v>0.1657337120714573</v>
+        <v>0.1917776342197825</v>
       </c>
       <c r="D26">
-        <v>0.1424283114349797</v>
+        <v>0.18187637712073079</v>
       </c>
       <c r="E26">
-        <v>0.1361005591527559</v>
+        <v>0.17372565078952909</v>
       </c>
       <c r="F26">
-        <v>0.2640384996949577</v>
+        <v>0.24983640088800041</v>
       </c>
       <c r="G26">
-        <v>0.2627595750630973</v>
+        <v>0.26413851538763522</v>
       </c>
       <c r="H26">
-        <v>0.2840299976735355</v>
+        <v>0.34651832671304778</v>
       </c>
       <c r="I26">
-        <v>0.3592951270780057</v>
+        <v>0.56103631904191142</v>
       </c>
       <c r="J26">
-        <v>0.381162371129824</v>
+        <v>0.4707592879951894</v>
       </c>
       <c r="K26">
-        <v>0.4396277223428823</v>
+        <v>0.46544477749241581</v>
       </c>
       <c r="L26">
-        <v>0.4908239396257388</v>
+        <v>0.50728249153952687</v>
       </c>
       <c r="M26">
-        <v>0.5395778741339956</v>
+        <v>0.60040042625119705</v>
       </c>
       <c r="N26">
-        <v>0.5979552736184721</v>
+        <v>0.67248529095882148</v>
       </c>
       <c r="O26">
-        <v>0.6833235170778074</v>
+        <v>0.74230755728660336</v>
       </c>
       <c r="P26">
-        <v>0.7539812645112663</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>adj_red_c(950,750,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>0.8495641700683384</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>41</v>
       </c>
       <c r="B27">
-        <v>0.1717882625908206</v>
+        <v>4.6866009934718761E-2</v>
       </c>
       <c r="C27">
-        <v>0.1430735270839106</v>
+        <v>0.19378262777558139</v>
       </c>
       <c r="D27">
-        <v>0.1651127534968155</v>
+        <v>0.1804893746848979</v>
       </c>
       <c r="E27">
-        <v>0.1582876267676291</v>
+        <v>0.17058078454246001</v>
       </c>
       <c r="F27">
-        <v>0.301282546720369</v>
+        <v>0.2294761844080144</v>
       </c>
       <c r="G27">
-        <v>0.3534522422322015</v>
+        <v>0.23008920383029741</v>
       </c>
       <c r="H27">
-        <v>0.4311043069110113</v>
+        <v>0.2485507047849117</v>
       </c>
       <c r="I27">
-        <v>0.5868374161687905</v>
+        <v>0.40962486602914328</v>
       </c>
       <c r="J27">
-        <v>0.64392918842961</v>
+        <v>0.34349793720711103</v>
       </c>
       <c r="K27">
-        <v>0.6684037161994251</v>
+        <v>0.29910169930474129</v>
       </c>
       <c r="L27">
-        <v>0.651055012746885</v>
+        <v>0.29112351515597501</v>
       </c>
       <c r="M27">
-        <v>0.6681792429563167</v>
+        <v>0.34295131432125492</v>
       </c>
       <c r="N27">
-        <v>0.705329907801415</v>
+        <v>0.35453208293590788</v>
       </c>
       <c r="O27">
-        <v>0.7990666565977538</v>
+        <v>0.40271238751335331</v>
       </c>
       <c r="P27">
-        <v>0.861240843421337</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
-        </is>
+        <v>0.43224383924651621</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>42</v>
       </c>
       <c r="B28">
-        <v>0.04057948458472652</v>
+        <v>4.211349595824581E-2</v>
       </c>
       <c r="C28">
-        <v>0.1618204323733578</v>
+        <v>0.16839320761407151</v>
       </c>
       <c r="D28">
-        <v>0.1969849765365562</v>
+        <v>0.2000593831772953</v>
       </c>
       <c r="E28">
-        <v>0.1971973976528395</v>
+        <v>0.19052697316246739</v>
       </c>
       <c r="F28">
-        <v>0.2356489192539993</v>
+        <v>0.19163771549334069</v>
       </c>
       <c r="G28">
-        <v>0.2228210113989856</v>
+        <v>0.20409619797230791</v>
       </c>
       <c r="H28">
-        <v>0.3406532440551215</v>
+        <v>0.2803837600103592</v>
       </c>
       <c r="I28">
-        <v>0.428778824730799</v>
+        <v>0.39460201004265782</v>
       </c>
       <c r="J28">
-        <v>0.4698527941911672</v>
+        <v>0.37614285439332068</v>
       </c>
       <c r="K28">
-        <v>0.4364028088605478</v>
+        <v>0.35058602814054912</v>
       </c>
       <c r="L28">
-        <v>0.4475970973977</v>
+        <v>0.31197423993546142</v>
       </c>
       <c r="M28">
-        <v>0.5355171151140157</v>
+        <v>0.31929242706023347</v>
       </c>
       <c r="N28">
-        <v>0.6594066472158383</v>
+        <v>0.36434400457661681</v>
       </c>
       <c r="O28">
-        <v>0.7326123668782587</v>
+        <v>0.41662832543469802</v>
       </c>
       <c r="P28">
-        <v>0.8304017733566105</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
-        </is>
+        <v>0.44214266755581949</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>43</v>
       </c>
       <c r="B29">
-        <v>0.04461081502281936</v>
+        <v>4.4827244514998602E-2</v>
       </c>
       <c r="C29">
-        <v>0.1792971141027531</v>
+        <v>0.17805542529352969</v>
       </c>
       <c r="D29">
-        <v>0.2112834136046649</v>
+        <v>0.20903391189848861</v>
       </c>
       <c r="E29">
-        <v>0.2088507904920523</v>
+        <v>0.20358081273753631</v>
       </c>
       <c r="F29">
-        <v>0.2114405898289305</v>
+        <v>0.19925835816931811</v>
       </c>
       <c r="G29">
-        <v>0.239739277175272</v>
+        <v>0.21133229957989819</v>
       </c>
       <c r="H29">
-        <v>0.3612376113069862</v>
+        <v>0.28351476484313071</v>
       </c>
       <c r="I29">
-        <v>0.5051471718760651</v>
+        <v>0.39925687154441741</v>
       </c>
       <c r="J29">
-        <v>0.4984190961905731</v>
+        <v>0.38786662946914241</v>
       </c>
       <c r="K29">
-        <v>0.4640885662436787</v>
+        <v>0.33293576339766762</v>
       </c>
       <c r="L29">
-        <v>0.4593256379687709</v>
+        <v>0.29413509472839028</v>
       </c>
       <c r="M29">
-        <v>0.4879610884339858</v>
+        <v>0.28733481221619078</v>
       </c>
       <c r="N29">
-        <v>0.5664910396228786</v>
+        <v>0.3297417624494044</v>
       </c>
       <c r="O29">
-        <v>0.6680424616064409</v>
+        <v>0.37137162691503522</v>
       </c>
       <c r="P29">
-        <v>0.7467623991321028</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
-        </is>
+        <v>0.39071330075140331</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>44</v>
       </c>
       <c r="B30">
-        <v>0.04071248360774892</v>
+        <v>4.2582388048687587E-2</v>
       </c>
       <c r="C30">
-        <v>0.1910677478584012</v>
+        <v>0.1728235495530889</v>
       </c>
       <c r="D30">
-        <v>0.1795028869907874</v>
+        <v>0.2072451292569098</v>
       </c>
       <c r="E30">
-        <v>0.1768892074159163</v>
+        <v>0.19940162893287691</v>
       </c>
       <c r="F30">
-        <v>0.2561325598332798</v>
+        <v>0.2012615744996937</v>
       </c>
       <c r="G30">
-        <v>0.2715673581461773</v>
+        <v>0.20804919405558789</v>
       </c>
       <c r="H30">
-        <v>0.3553515786396781</v>
+        <v>0.29401886604057992</v>
       </c>
       <c r="I30">
-        <v>0.5675965785528275</v>
+        <v>0.40841780206884609</v>
       </c>
       <c r="J30">
-        <v>0.4749450158737274</v>
+        <v>0.39712597415366868</v>
       </c>
       <c r="K30">
-        <v>0.4739402753245354</v>
+        <v>0.33719810849179321</v>
       </c>
       <c r="L30">
-        <v>0.5189355460817691</v>
+        <v>0.29971314553586942</v>
       </c>
       <c r="M30">
-        <v>0.6022955501931924</v>
+        <v>0.29325001000249712</v>
       </c>
       <c r="N30">
-        <v>0.6732595877671608</v>
+        <v>0.33598354446719292</v>
       </c>
       <c r="O30">
-        <v>0.7471460569946691</v>
+        <v>0.37085353046669289</v>
       </c>
       <c r="P30">
-        <v>0.8496031635239492</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-        </is>
+        <v>0.38228123576679052</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>45</v>
       </c>
       <c r="B31">
-        <v>0.04436686298211666</v>
+        <v>4.6681548562926951E-2</v>
       </c>
       <c r="C31">
-        <v>0.1917608507251619</v>
+        <v>0.17425611636893809</v>
       </c>
       <c r="D31">
-        <v>0.183232280578652</v>
+        <v>0.204116266617341</v>
       </c>
       <c r="E31">
-        <v>0.1676654594547975</v>
+        <v>0.19476625658934671</v>
       </c>
       <c r="F31">
-        <v>0.2255838948485056</v>
+        <v>0.19445513808551479</v>
       </c>
       <c r="G31">
-        <v>0.2304391221897258</v>
+        <v>0.19956656973244269</v>
       </c>
       <c r="H31">
-        <v>0.24859377770385</v>
+        <v>0.27271518007347051</v>
       </c>
       <c r="I31">
-        <v>0.4222297245427102</v>
+        <v>0.38044528844633002</v>
       </c>
       <c r="J31">
-        <v>0.3498787581249749</v>
+        <v>0.37413350623707442</v>
       </c>
       <c r="K31">
-        <v>0.3102612824454967</v>
+        <v>0.33483193815083861</v>
       </c>
       <c r="L31">
-        <v>0.298507082558955</v>
+        <v>0.29200916300835528</v>
       </c>
       <c r="M31">
-        <v>0.3448657481621842</v>
+        <v>0.28050290743325179</v>
       </c>
       <c r="N31">
-        <v>0.3643715471868081</v>
+        <v>0.31489993737410671</v>
       </c>
       <c r="O31">
-        <v>0.4092163652660056</v>
+        <v>0.36329223722445408</v>
       </c>
       <c r="P31">
-        <v>0.4361528838981067</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
-        </is>
+        <v>0.36786247058707039</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>46</v>
       </c>
       <c r="B32">
-        <v>0.04172277674150839</v>
+        <v>4.4212167943294862E-2</v>
       </c>
       <c r="C32">
-        <v>0.1718774683018272</v>
+        <v>0.1771401563336123</v>
       </c>
       <c r="D32">
-        <v>0.2055656442811605</v>
+        <v>0.21126807851294599</v>
       </c>
       <c r="E32">
-        <v>0.1977798721315083</v>
+        <v>0.2062935334679489</v>
       </c>
       <c r="F32">
-        <v>0.1956614350131901</v>
+        <v>0.20341998389180929</v>
       </c>
       <c r="G32">
-        <v>0.2103430787884324</v>
+        <v>0.21327167508060579</v>
       </c>
       <c r="H32">
-        <v>0.2870379025728904</v>
+        <v>0.30523067385558827</v>
       </c>
       <c r="I32">
-        <v>0.4060741522022123</v>
+        <v>0.40243597137035481</v>
       </c>
       <c r="J32">
-        <v>0.3891065487725651</v>
+        <v>0.38860894777145399</v>
       </c>
       <c r="K32">
-        <v>0.3559963416638259</v>
+        <v>0.36562841590156808</v>
       </c>
       <c r="L32">
-        <v>0.3063821618093588</v>
+        <v>0.32628207748539251</v>
       </c>
       <c r="M32">
-        <v>0.3113717399937131</v>
+        <v>0.32822848788765119</v>
       </c>
       <c r="N32">
-        <v>0.352134731140348</v>
+        <v>0.38439910109148101</v>
       </c>
       <c r="O32">
-        <v>0.4065446626229785</v>
+        <v>0.45371211201523293</v>
       </c>
       <c r="P32">
-        <v>0.4316691250039352</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
-        </is>
+        <v>0.50175986341143319</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>47</v>
       </c>
       <c r="B33">
-        <v>0.04282491829682174</v>
+        <v>4.5505479042098597E-2</v>
       </c>
       <c r="C33">
-        <v>0.1759380294119303</v>
+        <v>0.18211925653649599</v>
       </c>
       <c r="D33">
-        <v>0.2070095182790684</v>
+        <v>0.21719834197757251</v>
       </c>
       <c r="E33">
-        <v>0.1991419696498896</v>
+        <v>0.20948319316459019</v>
       </c>
       <c r="F33">
-        <v>0.1962786542403793</v>
+        <v>0.2039044279186091</v>
       </c>
       <c r="G33">
-        <v>0.2075095320005881</v>
+        <v>0.21654943762401349</v>
       </c>
       <c r="H33">
-        <v>0.2858517031641721</v>
+        <v>0.30233631196510807</v>
       </c>
       <c r="I33">
-        <v>0.3938268336022812</v>
+        <v>0.40547579228871689</v>
       </c>
       <c r="J33">
-        <v>0.382016296544759</v>
+        <v>0.39234386527550352</v>
       </c>
       <c r="K33">
-        <v>0.3285440057526851</v>
+        <v>0.34928797865364408</v>
       </c>
       <c r="L33">
-        <v>0.2918870528085471</v>
+        <v>0.31851012340609791</v>
       </c>
       <c r="M33">
-        <v>0.2933769333478792</v>
+        <v>0.31973847067991878</v>
       </c>
       <c r="N33">
-        <v>0.3326445324194995</v>
+        <v>0.37548588729120441</v>
       </c>
       <c r="O33">
-        <v>0.3715267439103312</v>
+        <v>0.43675684513612772</v>
       </c>
       <c r="P33">
-        <v>0.3933256028501858</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
-        </is>
+        <v>0.48912963705861368</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>48</v>
       </c>
       <c r="B34">
-        <v>0.04323031608997881</v>
+        <v>4.535176491416161E-2</v>
       </c>
       <c r="C34">
-        <v>0.1725896086472783</v>
+        <v>0.17755199433468799</v>
       </c>
       <c r="D34">
-        <v>0.2054811432623284</v>
+        <v>0.2122463128530851</v>
       </c>
       <c r="E34">
-        <v>0.1984654434491969</v>
+        <v>0.20664300573729399</v>
       </c>
       <c r="F34">
-        <v>0.1933089074114444</v>
+        <v>0.20328130922138421</v>
       </c>
       <c r="G34">
-        <v>0.1997128901097538</v>
+        <v>0.20990030642231289</v>
       </c>
       <c r="H34">
-        <v>0.2784015922771361</v>
+        <v>0.28885583296532941</v>
       </c>
       <c r="I34">
-        <v>0.3986812196206064</v>
+        <v>0.39738020115010653</v>
       </c>
       <c r="J34">
-        <v>0.3864546669592043</v>
+        <v>0.39319053381730262</v>
       </c>
       <c r="K34">
-        <v>0.3313415759482878</v>
+        <v>0.36514740091727099</v>
       </c>
       <c r="L34">
-        <v>0.2971851887094664</v>
+        <v>0.32536404830444199</v>
       </c>
       <c r="M34">
-        <v>0.2947141504589053</v>
+        <v>0.31698250748339862</v>
       </c>
       <c r="N34">
-        <v>0.3470825004563489</v>
+        <v>0.36328176519762728</v>
       </c>
       <c r="O34">
-        <v>0.3780087043952886</v>
+        <v>0.42075322473785232</v>
       </c>
       <c r="P34">
-        <v>0.4063027047820256</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
-        </is>
+        <v>0.45703131123563412</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>49</v>
       </c>
       <c r="B35">
-        <v>0.04527389952319913</v>
+        <v>4.3226666622369223E-2</v>
       </c>
       <c r="C35">
-        <v>0.1763058902150497</v>
+        <v>0.1764129593200581</v>
       </c>
       <c r="D35">
-        <v>0.2136019692511651</v>
+        <v>0.21007234646717499</v>
       </c>
       <c r="E35">
-        <v>0.2019415204175856</v>
+        <v>0.2044396313880287</v>
       </c>
       <c r="F35">
-        <v>0.2009334837947678</v>
+        <v>0.20550375220789691</v>
       </c>
       <c r="G35">
-        <v>0.2101041847141298</v>
+        <v>0.21365695896125311</v>
       </c>
       <c r="H35">
-        <v>0.2951607597196911</v>
+        <v>0.28694101428477797</v>
       </c>
       <c r="I35">
-        <v>0.4080311130731266</v>
+        <v>0.38983997704522261</v>
       </c>
       <c r="J35">
-        <v>0.4063734579382028</v>
+        <v>0.3810601092524209</v>
       </c>
       <c r="K35">
-        <v>0.3523975252478285</v>
+        <v>0.34242703566154847</v>
       </c>
       <c r="L35">
-        <v>0.3135723152882788</v>
+        <v>0.30444206491087072</v>
       </c>
       <c r="M35">
-        <v>0.2962620653303433</v>
+        <v>0.29706435849936041</v>
       </c>
       <c r="N35">
-        <v>0.331795445061404</v>
+        <v>0.33921778633555227</v>
       </c>
       <c r="O35">
-        <v>0.3778579781986472</v>
+        <v>0.39043592724883658</v>
       </c>
       <c r="P35">
-        <v>0.382854983629071</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-        </is>
+        <v>0.4246987272411783</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>50</v>
       </c>
       <c r="B36">
-        <v>0.0457456886195533</v>
+        <v>4.5158369765544062E-2</v>
       </c>
       <c r="C36">
-        <v>0.1812680454897064</v>
+        <v>0.17998507381897</v>
       </c>
       <c r="D36">
-        <v>0.214206274947531</v>
+        <v>0.21531338376472761</v>
       </c>
       <c r="E36">
-        <v>0.2056676051038841</v>
+        <v>0.2060357217781667</v>
       </c>
       <c r="F36">
-        <v>0.2079197061980149</v>
+        <v>0.2018327612738248</v>
       </c>
       <c r="G36">
-        <v>0.2224041913772364</v>
+        <v>0.20581834882753119</v>
       </c>
       <c r="H36">
-        <v>0.3057739225149511</v>
+        <v>0.2807242508363712</v>
       </c>
       <c r="I36">
-        <v>0.4229937368286139</v>
+        <v>0.37803662897243973</v>
       </c>
       <c r="J36">
-        <v>0.4060224531909635</v>
+        <v>0.37674078261705901</v>
       </c>
       <c r="K36">
-        <v>0.3700547970726564</v>
+        <v>0.33960986406338822</v>
       </c>
       <c r="L36">
-        <v>0.3235314912991337</v>
+        <v>0.31009258047676569</v>
       </c>
       <c r="M36">
-        <v>0.3213135693927744</v>
+        <v>0.28942747592699419</v>
       </c>
       <c r="N36">
-        <v>0.3818524276380806</v>
+        <v>0.31225995938357648</v>
       </c>
       <c r="O36">
-        <v>0.4491288036333294</v>
+        <v>0.35989239798988282</v>
       </c>
       <c r="P36">
-        <v>0.4997330511833563</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
-        </is>
+        <v>0.37093922601934309</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>51</v>
       </c>
       <c r="B37">
-        <v>0.04349823847893455</v>
+        <v>5.2182177506884253E-2</v>
       </c>
       <c r="C37">
-        <v>0.1679279626985467</v>
+        <v>0.30543514924227472</v>
       </c>
       <c r="D37">
-        <v>0.1997592940396759</v>
+        <v>0.27571231646660749</v>
       </c>
       <c r="E37">
-        <v>0.1943789832013953</v>
+        <v>0.30264364698466018</v>
       </c>
       <c r="F37">
-        <v>0.1939896584912109</v>
+        <v>0.48487255528091888</v>
       </c>
       <c r="G37">
-        <v>0.2030036859104578</v>
+        <v>0.55786361603383239</v>
       </c>
       <c r="H37">
-        <v>0.2889199300188955</v>
+        <v>0.58220123419083614</v>
       </c>
       <c r="I37">
-        <v>0.4040001736430521</v>
+        <v>0.5954722690002765</v>
       </c>
       <c r="J37">
-        <v>0.3885214252503804</v>
+        <v>0.63636047789801731</v>
       </c>
       <c r="K37">
-        <v>0.3628045549126057</v>
+        <v>0.67466514213101869</v>
       </c>
       <c r="L37">
-        <v>0.3201523525116786</v>
+        <v>0.7242395462425093</v>
       </c>
       <c r="M37">
-        <v>0.3152154069722568</v>
+        <v>0.79868911376136276</v>
       </c>
       <c r="N37">
-        <v>0.3763720772631609</v>
+        <v>0.78899007949393096</v>
       </c>
       <c r="O37">
-        <v>0.4393036356329755</v>
+        <v>0.78327446142851687</v>
       </c>
       <c r="P37">
-        <v>0.4890038670516005</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
-        </is>
+        <v>0.77907360308833162</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>52</v>
       </c>
       <c r="B38">
-        <v>0.04155257187642281</v>
+        <v>4.7296092955685258E-2</v>
       </c>
       <c r="C38">
-        <v>0.1738352873460395</v>
+        <v>0.22926865658027351</v>
       </c>
       <c r="D38">
-        <v>0.2027772080366751</v>
+        <v>0.226809746544264</v>
       </c>
       <c r="E38">
-        <v>0.19249090363431</v>
+        <v>0.27280878442404438</v>
       </c>
       <c r="F38">
-        <v>0.1934482051786397</v>
+        <v>0.38360148767232949</v>
       </c>
       <c r="G38">
-        <v>0.2027820336927711</v>
+        <v>0.36053041958921961</v>
       </c>
       <c r="H38">
-        <v>0.271570517022759</v>
+        <v>0.26554790358197888</v>
       </c>
       <c r="I38">
-        <v>0.3939673313103978</v>
+        <v>0.32464749236925938</v>
       </c>
       <c r="J38">
-        <v>0.3824915827064386</v>
+        <v>0.41723027793056422</v>
       </c>
       <c r="K38">
-        <v>0.3550134391850555</v>
+        <v>0.46735594900722249</v>
       </c>
       <c r="L38">
-        <v>0.3184820545706545</v>
+        <v>0.50126693721420956</v>
       </c>
       <c r="M38">
-        <v>0.3178890894678963</v>
+        <v>0.53334832094935847</v>
       </c>
       <c r="N38">
-        <v>0.3618187077667476</v>
+        <v>0.53806970937910359</v>
       </c>
       <c r="O38">
-        <v>0.4135379065633435</v>
+        <v>0.54968173045164481</v>
       </c>
       <c r="P38">
-        <v>0.4553120599069815</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-        </is>
+        <v>0.5661758356559895</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>53</v>
       </c>
       <c r="B39">
-        <v>0.04555977682679271</v>
+        <v>4.9029678666618698E-2</v>
       </c>
       <c r="C39">
-        <v>0.1773911507470628</v>
+        <v>0.2255963730668171</v>
       </c>
       <c r="D39">
-        <v>0.2081991979765494</v>
+        <v>0.2130788244235447</v>
       </c>
       <c r="E39">
-        <v>0.2008381406787607</v>
+        <v>0.22322455484701251</v>
       </c>
       <c r="F39">
-        <v>0.1949828596321797</v>
+        <v>0.30781716624645988</v>
       </c>
       <c r="G39">
-        <v>0.2077304560472407</v>
+        <v>0.29339340681274101</v>
       </c>
       <c r="H39">
-        <v>0.2987582108309231</v>
+        <v>0.25363966465276122</v>
       </c>
       <c r="I39">
-        <v>0.3970494273833071</v>
+        <v>0.29190198959078989</v>
       </c>
       <c r="J39">
-        <v>0.3799856812141312</v>
+        <v>0.34759398137579761</v>
       </c>
       <c r="K39">
-        <v>0.3633884334054094</v>
+        <v>0.36653656431462739</v>
       </c>
       <c r="L39">
-        <v>0.3236460845061883</v>
+        <v>0.39699726786775502</v>
       </c>
       <c r="M39">
-        <v>0.3170482733570179</v>
+        <v>0.40508446177099389</v>
       </c>
       <c r="N39">
-        <v>0.3613415599965075</v>
+        <v>0.44567883868674579</v>
       </c>
       <c r="O39">
-        <v>0.4164314239919631</v>
+        <v>0.48611755469402312</v>
       </c>
       <c r="P39">
-        <v>0.4509523533264242</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-        </is>
+        <v>0.51294198020782478</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>54</v>
       </c>
       <c r="B40">
-        <v>0.04639227603773026</v>
+        <v>7.6902923184229699E-2</v>
       </c>
       <c r="C40">
-        <v>0.1718928971501663</v>
+        <v>0.12841731980223409</v>
       </c>
       <c r="D40">
-        <v>0.2017940867480949</v>
+        <v>0.2129539871055694</v>
       </c>
       <c r="E40">
-        <v>0.1929674213687571</v>
+        <v>0.27540052019382322</v>
       </c>
       <c r="F40">
-        <v>0.1918130265030843</v>
+        <v>0.3547200493242238</v>
       </c>
       <c r="G40">
-        <v>0.2039255024664994</v>
+        <v>0.37198495433414769</v>
       </c>
       <c r="H40">
-        <v>0.2764138293481136</v>
+        <v>0.46221637996410331</v>
       </c>
       <c r="I40">
-        <v>0.3814440864664244</v>
+        <v>0.5940245660190655</v>
       </c>
       <c r="J40">
-        <v>0.3737119048227646</v>
+        <v>0.62188482793877942</v>
       </c>
       <c r="K40">
-        <v>0.332578994745943</v>
+        <v>0.62060106476957588</v>
       </c>
       <c r="L40">
-        <v>0.3051825656125159</v>
+        <v>0.63299291912329303</v>
       </c>
       <c r="M40">
-        <v>0.294184632074025</v>
+        <v>0.62758018157849393</v>
       </c>
       <c r="N40">
-        <v>0.3173948291344849</v>
+        <v>0.65378350984436295</v>
       </c>
       <c r="O40">
-        <v>0.3682326724397665</v>
+        <v>0.70693998816298831</v>
       </c>
       <c r="P40">
-        <v>0.3742774468204298</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-        </is>
+        <v>0.78766504909410973</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>55</v>
       </c>
       <c r="B41">
-        <v>0.05432047564549737</v>
+        <v>0.10916726126708549</v>
       </c>
       <c r="C41">
-        <v>0.3049164860778549</v>
+        <v>0.44397830868153643</v>
       </c>
       <c r="D41">
-        <v>0.2736498488468602</v>
+        <v>0.50771809070157414</v>
       </c>
       <c r="E41">
-        <v>0.3175838850125459</v>
+        <v>0.62785109359541025</v>
       </c>
       <c r="F41">
-        <v>0.5047921725479398</v>
+        <v>0.64748939648289039</v>
       </c>
       <c r="G41">
-        <v>0.5664847338429557</v>
+        <v>0.6874775733687829</v>
       </c>
       <c r="H41">
-        <v>0.5891374901243547</v>
+        <v>0.72689472633727858</v>
       </c>
       <c r="I41">
-        <v>0.5906777542797979</v>
+        <v>0.68707803499460252</v>
       </c>
       <c r="J41">
-        <v>0.636353443156788</v>
+        <v>0.76255262608284524</v>
       </c>
       <c r="K41">
-        <v>0.6648083153805608</v>
+        <v>0.83232878195953575</v>
       </c>
       <c r="L41">
-        <v>0.7120091150579537</v>
+        <v>0.85027807545871437</v>
       </c>
       <c r="M41">
-        <v>0.7921886657350313</v>
+        <v>0.91768821081186791</v>
       </c>
       <c r="N41">
-        <v>0.7803564699402451</v>
+        <v>0.99977819871984952</v>
       </c>
       <c r="O41">
-        <v>0.7710011043792375</v>
+        <v>1.018662539929776</v>
       </c>
       <c r="P41">
-        <v>0.7701797214967647</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
-        </is>
+        <v>1.0467001420543851</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>56</v>
       </c>
       <c r="B42">
-        <v>0.05137509443802854</v>
+        <v>6.5142627660439156E-2</v>
       </c>
       <c r="C42">
-        <v>0.2360574096328902</v>
+        <v>0.20208976074397261</v>
       </c>
       <c r="D42">
-        <v>0.233396471215538</v>
+        <v>0.53357475935146637</v>
       </c>
       <c r="E42">
-        <v>0.2657566016303736</v>
+        <v>0.43931685126454129</v>
       </c>
       <c r="F42">
-        <v>0.3762446177672485</v>
+        <v>0.43842701297349479</v>
       </c>
       <c r="G42">
-        <v>0.3515616027960858</v>
+        <v>0.45854462066192048</v>
       </c>
       <c r="H42">
-        <v>0.2699666248656553</v>
+        <v>0.39977133186597219</v>
       </c>
       <c r="I42">
-        <v>0.3255388802144954</v>
+        <v>0.43443645867027531</v>
       </c>
       <c r="J42">
-        <v>0.4222400646698112</v>
+        <v>0.47581900052944281</v>
       </c>
       <c r="K42">
-        <v>0.4750892063533314</v>
+        <v>0.45736368340531058</v>
       </c>
       <c r="L42">
-        <v>0.5200532121993533</v>
+        <v>0.47626753994997362</v>
       </c>
       <c r="M42">
-        <v>0.54225071659226</v>
+        <v>0.52044329814833579</v>
       </c>
       <c r="N42">
-        <v>0.545437272836482</v>
+        <v>0.55528411181354642</v>
       </c>
       <c r="O42">
-        <v>0.5533990545995595</v>
+        <v>0.56253082501378415</v>
       </c>
       <c r="P42">
-        <v>0.5688157469196896</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-        </is>
+        <v>0.59396558384529841</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>57</v>
       </c>
       <c r="B43">
-        <v>0.04722264403150864</v>
+        <v>5.6621402640376101E-2</v>
       </c>
       <c r="C43">
-        <v>0.2243783614098249</v>
+        <v>0.23776440477484159</v>
       </c>
       <c r="D43">
-        <v>0.2059151097341408</v>
+        <v>0.39399949844648041</v>
       </c>
       <c r="E43">
-        <v>0.222416138351032</v>
+        <v>0.40589939890633309</v>
       </c>
       <c r="F43">
-        <v>0.3068234314415367</v>
+        <v>0.35953529952127339</v>
       </c>
       <c r="G43">
-        <v>0.2883934696935256</v>
+        <v>0.36945234516268921</v>
       </c>
       <c r="H43">
-        <v>0.2555970595343637</v>
+        <v>0.37534985076639071</v>
       </c>
       <c r="I43">
-        <v>0.2864417963807444</v>
+        <v>0.4203814515417163</v>
       </c>
       <c r="J43">
-        <v>0.3590444920623713</v>
+        <v>0.51187531349184878</v>
       </c>
       <c r="K43">
-        <v>0.3741343639197995</v>
+        <v>0.5245405488884588</v>
       </c>
       <c r="L43">
-        <v>0.4108804789865962</v>
+        <v>0.5450837749492794</v>
       </c>
       <c r="M43">
-        <v>0.4186320795935747</v>
+        <v>0.57995924391190212</v>
       </c>
       <c r="N43">
-        <v>0.4528903507404125</v>
+        <v>0.61961779170056508</v>
       </c>
       <c r="O43">
-        <v>0.4852552936141985</v>
+        <v>0.66365780750112591</v>
       </c>
       <c r="P43">
-        <v>0.5099243241761171</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
-        </is>
-      </c>
-      <c r="B44">
-        <v>0.08979066199600708</v>
-      </c>
-      <c r="C44">
-        <v>0.1472738214290659</v>
-      </c>
-      <c r="D44">
-        <v>0.2201153114811452</v>
-      </c>
-      <c r="E44">
-        <v>0.2899603577921401</v>
-      </c>
-      <c r="F44">
-        <v>0.3626934866553616</v>
-      </c>
-      <c r="G44">
-        <v>0.3742145627519486</v>
-      </c>
-      <c r="H44">
-        <v>0.4742428028216558</v>
-      </c>
-      <c r="I44">
-        <v>0.6067027776668413</v>
-      </c>
-      <c r="J44">
-        <v>0.6325871304113777</v>
-      </c>
-      <c r="K44">
-        <v>0.6330649017941042</v>
-      </c>
-      <c r="L44">
-        <v>0.643909906164314</v>
-      </c>
-      <c r="M44">
-        <v>0.6387285118744379</v>
-      </c>
-      <c r="N44">
-        <v>0.6683935828841713</v>
-      </c>
-      <c r="O44">
-        <v>0.7189574028253837</v>
-      </c>
-      <c r="P44">
-        <v>0.7928533657106144</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>adj_snv_sder_c(1,3,5)_</t>
-        </is>
-      </c>
-      <c r="B45">
-        <v>0.1058896206023202</v>
-      </c>
-      <c r="C45">
-        <v>0.4410850712289234</v>
-      </c>
-      <c r="D45">
-        <v>0.5003971710068746</v>
-      </c>
-      <c r="E45">
-        <v>0.6282526140637813</v>
-      </c>
-      <c r="F45">
-        <v>0.6437224356871538</v>
-      </c>
-      <c r="G45">
-        <v>0.6855215167918421</v>
-      </c>
-      <c r="H45">
-        <v>0.7130817161397296</v>
-      </c>
-      <c r="I45">
-        <v>0.6808356507027383</v>
-      </c>
-      <c r="J45">
-        <v>0.7544115951662126</v>
-      </c>
-      <c r="K45">
-        <v>0.8281414869826106</v>
-      </c>
-      <c r="L45">
-        <v>0.8398971184299571</v>
-      </c>
-      <c r="M45">
-        <v>0.9024050318672439</v>
-      </c>
-      <c r="N45">
-        <v>0.981935856476256</v>
-      </c>
-      <c r="O45">
-        <v>1.004031235956375</v>
-      </c>
-      <c r="P45">
-        <v>1.024946856598736</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>adj_snv_sder_c(2,3,15)_</t>
-        </is>
-      </c>
-      <c r="B46">
-        <v>0.06377474949620875</v>
-      </c>
-      <c r="C46">
-        <v>0.189594248909405</v>
-      </c>
-      <c r="D46">
-        <v>0.5293744472987849</v>
-      </c>
-      <c r="E46">
-        <v>0.4193143533626466</v>
-      </c>
-      <c r="F46">
-        <v>0.4245558048059807</v>
-      </c>
-      <c r="G46">
-        <v>0.4567855391576644</v>
-      </c>
-      <c r="H46">
-        <v>0.3940960817792182</v>
-      </c>
-      <c r="I46">
-        <v>0.4338331877671582</v>
-      </c>
-      <c r="J46">
-        <v>0.4742329550980144</v>
-      </c>
-      <c r="K46">
-        <v>0.4609181643633954</v>
-      </c>
-      <c r="L46">
-        <v>0.4803032352449623</v>
-      </c>
-      <c r="M46">
-        <v>0.5226968689199727</v>
-      </c>
-      <c r="N46">
-        <v>0.5550735780129513</v>
-      </c>
-      <c r="O46">
-        <v>0.5621846494759278</v>
-      </c>
-      <c r="P46">
-        <v>0.6009431909895053</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
-        </is>
-      </c>
-      <c r="B47">
-        <v>0.05579290190224231</v>
-      </c>
-      <c r="C47">
-        <v>0.231114180643085</v>
-      </c>
-      <c r="D47">
-        <v>0.3890874746400782</v>
-      </c>
-      <c r="E47">
-        <v>0.4018955727375099</v>
-      </c>
-      <c r="F47">
-        <v>0.3583000568902831</v>
-      </c>
-      <c r="G47">
-        <v>0.3727986642218555</v>
-      </c>
-      <c r="H47">
-        <v>0.3758687341271569</v>
-      </c>
-      <c r="I47">
-        <v>0.4164878341761598</v>
-      </c>
-      <c r="J47">
-        <v>0.5035788361327326</v>
-      </c>
-      <c r="K47">
-        <v>0.5250790671107857</v>
-      </c>
-      <c r="L47">
-        <v>0.5413269701550358</v>
-      </c>
-      <c r="M47">
-        <v>0.5755306870862574</v>
-      </c>
-      <c r="N47">
-        <v>0.6233694240826435</v>
-      </c>
-      <c r="O47">
-        <v>0.6653932707161645</v>
-      </c>
-      <c r="P47">
-        <v>0.7064732073585052</v>
+        <v>0.69605406817007354</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B2:P43">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
+      <formula>0.2</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
+      <formula>0.2</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>